--- a/stories/arbres/TREE-DIF-006.xlsx
+++ b/stories/arbres/TREE-DIF-006.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1163,7 +1180,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Adam est dans le jardin, avec papa. Maman arrose une fleur. Un camarade court, saute, tourne. Il a beaucoup d'énergie. Papa dit : cette énergie n'est pas une faute. On peut jouer ou attendre. On peut jouer ensemble.</t>
+          <t>Adam est dans le jardin, avec papa. Maman arrose une fleur. Un camarade court, saute, tourne. Il a beaucoup d'énergie. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut jouer ensemble.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1301,6 +1318,12 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Adam est dans le jardin, avec papa. Maman arrose une fleur. Un camarade court, saute, tourne. Il a beaucoup d'énergie.
+papa|Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1489,6 +1512,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -1653,6 +1681,11 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint Tom. Tom court autour du bac. Il a beaucoup d'énergie. Cette énergie n'est pas une faute. Adam peut jouer ou attendre. Papa est là. Tom s'arrête, puis reprend. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1833,6 +1866,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Beaucoup d'énergie, c'est une faute ?</t>
         </is>
       </c>
     </row>
@@ -2001,6 +2039,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Cette énergie n'est pas une faute. On peut jouer ou attendre. Adam respire. Papa est là. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2187,6 +2230,11 @@
         <v>8</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2349,6 +2397,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Tom veut les cubes. Il bouge beaucoup. Cette énergie n'est pas une faute. Adam peut jouer ou attendre. Papa montre le geste, lentement. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2535,6 +2588,11 @@
         <v>8</v>
       </c>
       <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2697,6 +2755,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Adam a choisi Tom. Puis les cubes. Puis une pomme. Une pomme brille un peu. Adam dit merci à papa. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Adam dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2859,6 +2922,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3021,6 +3089,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Adam s'arrête près de un yaourt. les cubes est rangé. Les chaussures font toc toc. Adam enfile ses chaussons. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Adam dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3183,6 +3256,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3345,6 +3423,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Adam se souvient de Tom. Et de les cubes. Et de un morceau de pain. Une cloche tinte, tout loin. Adam montre un morceau de pain à papa. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Adam dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3507,6 +3590,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3531,7 +3619,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Tom veut le livre. Il tourne les pages vite. Cette énergie n'est pas une faute. Adam peut jouer ou attendre. Papa dit : je suis là. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut jouer ensemble.</t>
+          <t>Tom veut le livre. Il tourne les pages vite. Cette énergie n'est pas une faute. Adam peut jouer ou attendre. Je suis là. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut jouer ensemble.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -3669,6 +3757,12 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Tom veut le livre. Il tourne les pages vite. Cette énergie n'est pas une faute. Adam peut jouer ou attendre.
+papa|Je suis là. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3855,6 +3949,11 @@
         <v>8</v>
       </c>
       <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4017,6 +4116,11 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Avec une pomme. Après le livre. Près de Tom. Adam s'arrête. On rit un peu. Adam s'assoit près de papa. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Adam dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4179,6 +4283,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4341,6 +4450,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Adam range le livre. un yaourt reste près de Tom. Il y a des miettes sur la table. Adam range Tom dans sa tête, comme un souvenir. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Adam dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4503,6 +4617,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4527,7 +4646,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>un morceau de pain est là. le livre aussi. Tom reste dans le souvenir. La couverture est douce. Adam pose le livre à sa place. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Adam dit merci à papa.</t>
+          <t>Un morceau de pain est là. le livre aussi. Tom reste dans le souvenir. La couverture est douce. Adam pose le livre à sa place. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Adam dit merci à papa.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -4665,6 +4784,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Un morceau de pain est là. le livre aussi. Tom reste dans le souvenir. La couverture est douce. Adam pose le livre à sa place. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Adam dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4827,6 +4951,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4989,6 +5118,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Tom veut la dînette. Il range et dérange. Cette énergie n'est pas une faute. Adam peut jouer ou attendre. Papa reste tout près. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5175,6 +5309,11 @@
         <v>8</v>
       </c>
       <c r="AV25" s="2" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5337,6 +5476,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint une pomme. la dînette est rangé. Tom est fini. On se tient la main. Adam chuchote : c'est fini. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Adam dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5499,6 +5643,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5661,6 +5810,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Près de un yaourt. Adam pose la dînette. Tom est derrière. Un chat miaule une fois. Adam souffle, puis sourit à papa. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Adam dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5823,6 +5977,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5985,6 +6144,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Adam montre un morceau de pain. Papa a vu Tom. Et la dînette. Un linge sèche à l'air. Adam caresse le doudou. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Adam dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6147,6 +6311,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6171,7 +6340,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Adam rejoint Léa. Léa saute sur place. Elle a beaucoup d'énergie. Cette énergie n'est pas une faute. Adam peut jouer ou attendre. Maman dit : on peut demander à un adulte. On peut jouer ensemble.</t>
+          <t>Adam rejoint Léa. Léa saute sur place. Elle a beaucoup d'énergie. Cette énergie n'est pas une faute. Adam peut jouer ou attendre. On peut demander à un adulte. On peut jouer ensemble.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6309,6 +6478,12 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint Léa. Léa saute sur place. Elle a beaucoup d'énergie. Cette énergie n'est pas une faute. Adam peut jouer ou attendre.
+maman|On peut demander à un adulte. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6485,6 +6660,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|On joue, ou on attend ?</t>
         </is>
       </c>
     </row>
@@ -6653,6 +6833,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Cette énergie n'est pas une faute. On peut jouer ou attendre. Adam retient le geste. Papa sourit. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6839,6 +7024,11 @@
         <v>8</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -6863,7 +7053,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Léa veut les cubes. Elle saute. Cette énergie n'est pas une faute. Adam peut jouer ou attendre. Papa dit : je suis là. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut jouer ensemble.</t>
+          <t>Léa veut les cubes. Elle saute. Cette énergie n'est pas une faute. Adam peut jouer ou attendre. Je suis là. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut jouer ensemble.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -7001,6 +7191,12 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Léa veut les cubes. Elle saute. Cette énergie n'est pas une faute. Adam peut jouer ou attendre.
+papa|Je suis là. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7187,6 +7383,11 @@
         <v>8</v>
       </c>
       <c r="AV37" s="2" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7349,6 +7550,11 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Adam a choisi Léa. Puis les cubes. Puis une pomme. Un ruban reste dans la poche. Adam plie un pull. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Adam dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7511,6 +7717,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7673,6 +7884,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Adam s'arrête près de un yaourt. les cubes est rangé. Un ballon s'immobilise. Adam répète tout bas le geste. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Adam dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7835,6 +8051,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -7997,6 +8218,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Adam se souvient de Léa. Et de les cubes. Et de un morceau de pain. Le vent est doux. Adam serre la main de papa. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Adam dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8159,6 +8385,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8321,6 +8552,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Léa veut le livre. Elle pointe partout. Cette énergie n'est pas une faute. Adam peut jouer ou attendre. Papa reste tout près. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8507,6 +8743,11 @@
         <v>8</v>
       </c>
       <c r="AV45" s="2" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8669,6 +8910,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Avec une pomme. Après le livre. Près de Léa. Adam s'arrête. On range un objet. Adam pose sa tête un moment. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Adam dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8831,6 +9077,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -8993,6 +9244,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Adam range le livre. un yaourt reste près de Léa. On souffle doucement. Adam tend un yaourt à maman. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Adam dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9155,6 +9411,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9179,7 +9440,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>un morceau de pain est là. le livre aussi. Léa reste dans le souvenir. Une feuille tombe. Adam sourit. Papa sourit aussi. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Adam dit merci à papa.</t>
+          <t>Un morceau de pain est là. le livre aussi. Léa reste dans le souvenir. Une feuille tombe. Adam sourit. Papa sourit aussi. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Adam dit merci à papa.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -9317,6 +9578,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Un morceau de pain est là. le livre aussi. Léa reste dans le souvenir. Une feuille tombe. Adam sourit. Papa sourit aussi. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Adam dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9479,6 +9745,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9641,6 +9912,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Léa veut la dînette. Elle fait cliqueter. Cette énergie n'est pas une faute. Adam peut jouer ou attendre. Papa montre le geste, lentement. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9827,6 +10103,11 @@
         <v>8</v>
       </c>
       <c r="AV53" s="2" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -9989,6 +10270,11 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint une pomme. la dînette est rangé. Léa est fini. Le sol est un peu froid. Maman n'est pas loin. Adam les rejoint. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Adam dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10151,6 +10437,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10313,6 +10604,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Près de un yaourt. Adam pose la dînette. Léa est derrière. Ça sent le pain chaud. Adam range la tasse. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Adam dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10475,6 +10771,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10637,6 +10938,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Adam montre un morceau de pain. Papa a vu Léa. Et la dînette. On dit merci. Adam essuie ses mains. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Adam dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10799,6 +11105,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10961,6 +11272,11 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint Sami. Sami tourne, puis s'assoit. Il a beaucoup d'énergie. Cette énergie n'est pas une faute. Adam joue un moment, puis attend. Papa reste tout près. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11137,6 +11453,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|On demande à un adulte ?</t>
         </is>
       </c>
     </row>
@@ -11305,6 +11626,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Cette énergie n'est pas une faute. On peut jouer ou attendre. Adam hoche la tête. On continue, avec papa. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11491,6 +11817,11 @@
         <v>8</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11653,6 +11984,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Sami veut les cubes. Il court les chercher. Cette énergie n'est pas une faute. Adam peut jouer ou attendre. Papa reste tout près. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11839,6 +12175,11 @@
         <v>8</v>
       </c>
       <c r="AV65" s="2" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -11863,7 +12204,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Adam a choisi Sami. Puis les cubes. Puis une pomme. Un crochet tient bien le manteau. Adam dit : j'ai appris. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Adam dit merci à papa.</t>
+          <t>Adam a choisi Sami. Puis les cubes. Puis une pomme. Un crochet tient bien le manteau. J'ai appris. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Adam dit merci à papa.</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -12001,6 +12342,13 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Adam a choisi Sami. Puis les cubes. Puis une pomme. Un crochet tient bien le manteau.
+enfant-m|J'ai appris. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte.
+narrateur|Adam dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12163,6 +12511,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12325,6 +12678,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Adam s'arrête près de un yaourt. les cubes est rangé. L'eau coule, tout petit bruit. Adam ferme la porte, tout doux. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Adam dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12487,6 +12845,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12649,6 +13012,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Adam se souvient de Sami. Et de les cubes. Et de un morceau de pain. La lumière est claire. Adam marche près de papa. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Adam dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12811,6 +13179,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -12973,6 +13346,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Sami veut le livre. Il s'assoit, puis se lève. Cette énergie n'est pas une faute. Adam peut jouer ou attendre. Papa montre le geste, lentement. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13159,6 +13537,11 @@
         <v>8</v>
       </c>
       <c r="AV73" s="2" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13321,6 +13704,11 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Avec une pomme. Après le livre. Près de Sami. Adam s'arrête. Un vélo passe au loin. Adam écoute papa encore une fois. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Adam dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13483,6 +13871,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13645,6 +14038,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Adam range le livre. un yaourt reste près de Sami. Une chaussette est encore sablée. Adam ferme le sac. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Adam dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13807,6 +14205,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13831,7 +14234,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>un morceau de pain est là. le livre aussi. Sami reste dans le souvenir. Une tasse cliquette. Adam raccroche un linge. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Adam dit merci à papa.</t>
+          <t>Un morceau de pain est là. le livre aussi. Sami reste dans le souvenir. Une tasse cliquette. Adam raccroche un linge. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Adam dit merci à papa.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -13969,6 +14372,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Un morceau de pain est là. le livre aussi. Sami reste dans le souvenir. Une tasse cliquette. Adam raccroche un linge. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Adam dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14131,6 +14539,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14155,7 +14568,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Sami veut la dînette. Il sert très vite. Cette énergie n'est pas une faute. Adam peut jouer ou attendre. Papa dit : je suis là. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut jouer ensemble.</t>
+          <t>Sami veut la dînette. Il sert très vite. Cette énergie n'est pas une faute. Adam peut jouer ou attendre. Je suis là. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut jouer ensemble.</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -14293,6 +14706,12 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Sami veut la dînette. Il sert très vite. Cette énergie n'est pas une faute. Adam peut jouer ou attendre.
+papa|Je suis là. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14479,6 +14898,11 @@
         <v>8</v>
       </c>
       <c r="AV81" s="2" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14641,6 +15065,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint une pomme. la dînette est rangé. Sami est fini. Un panier est posé sur le banc. Adam boit une gorgée d'eau. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Adam dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14803,6 +15232,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -14965,6 +15399,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Près de un yaourt. Adam pose la dînette. Sami est derrière. On attend son tour. Adam prend la main de papa. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Adam dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15127,6 +15566,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15289,6 +15733,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Adam montre un morceau de pain. Papa a vu Sami. Et la dînette. Un galet est encore chaud. Adam range encore un peu, près de papa. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Adam dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15451,6 +15900,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15469,7 +15923,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15486,6 +15940,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>ch1: prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-DIF-006.xlsx
+++ b/stories/arbres/TREE-DIF-006.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1324,6 +1329,7 @@
 papa|Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1519,6 +1525,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1686,6 +1693,7 @@
           <t>narrateur|Adam rejoint Tom. Tom court autour du bac. Il a beaucoup d'énergie. Cette énergie n'est pas une faute. Adam peut jouer ou attendre. Papa est là. Tom s'arrête, puis reprend. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1873,6 +1881,7 @@
           <t>narrateur|Beaucoup d'énergie, c'est une faute ?</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2044,6 +2053,7 @@
           <t>narrateur|Oui. Cette énergie n'est pas une faute. On peut jouer ou attendre. Adam respire. Papa est là. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2235,6 +2245,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2402,6 +2413,7 @@
           <t>narrateur|Tom veut les cubes. Il bouge beaucoup. Cette énergie n'est pas une faute. Adam peut jouer ou attendre. Papa montre le geste, lentement. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2593,6 +2605,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2760,6 +2773,7 @@
           <t>narrateur|Adam a choisi Tom. Puis les cubes. Puis une pomme. Une pomme brille un peu. Adam dit merci à papa. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Adam dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2927,6 +2941,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3094,6 +3109,7 @@
           <t>narrateur|Adam s'arrête près de un yaourt. les cubes est rangé. Les chaussures font toc toc. Adam enfile ses chaussons. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Adam dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3261,6 +3277,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3428,6 +3445,7 @@
           <t>narrateur|Adam se souvient de Tom. Et de les cubes. Et de un morceau de pain. Une cloche tinte, tout loin. Adam montre un morceau de pain à papa. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Adam dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3595,6 +3613,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3763,6 +3782,7 @@
 papa|Je suis là. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3954,6 +3974,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4121,6 +4142,7 @@
           <t>narrateur|Avec une pomme. Après le livre. Près de Tom. Adam s'arrête. On rit un peu. Adam s'assoit près de papa. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Adam dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4288,6 +4310,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4455,6 +4478,7 @@
           <t>narrateur|Adam range le livre. un yaourt reste près de Tom. Il y a des miettes sur la table. Adam range Tom dans sa tête, comme un souvenir. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Adam dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4622,6 +4646,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4789,6 +4814,7 @@
           <t>narrateur|Un morceau de pain est là. le livre aussi. Tom reste dans le souvenir. La couverture est douce. Adam pose le livre à sa place. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Adam dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4956,6 +4982,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5123,6 +5150,7 @@
           <t>narrateur|Tom veut la dînette. Il range et dérange. Cette énergie n'est pas une faute. Adam peut jouer ou attendre. Papa reste tout près. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5314,6 +5342,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5481,6 +5510,7 @@
           <t>narrateur|Adam rejoint une pomme. la dînette est rangé. Tom est fini. On se tient la main. Adam chuchote : c'est fini. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Adam dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5648,6 +5678,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5815,6 +5846,7 @@
           <t>narrateur|Près de un yaourt. Adam pose la dînette. Tom est derrière. Un chat miaule une fois. Adam souffle, puis sourit à papa. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Adam dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5982,6 +6014,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6149,6 +6182,7 @@
           <t>narrateur|Adam montre un morceau de pain. Papa a vu Tom. Et la dînette. Un linge sèche à l'air. Adam caresse le doudou. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Adam dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6316,6 +6350,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6484,6 +6519,7 @@
 maman|On peut demander à un adulte. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6667,6 +6703,7 @@
           <t>narrateur|On joue, ou on attend ?</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6838,6 +6875,7 @@
           <t>narrateur|Oui. Cette énergie n'est pas une faute. On peut jouer ou attendre. Adam retient le geste. Papa sourit. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7029,6 +7067,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7197,6 +7236,7 @@
 papa|Je suis là. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7388,6 +7428,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7555,6 +7596,7 @@
           <t>narrateur|Adam a choisi Léa. Puis les cubes. Puis une pomme. Un ruban reste dans la poche. Adam plie un pull. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Adam dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7722,6 +7764,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7889,6 +7932,7 @@
           <t>narrateur|Adam s'arrête près de un yaourt. les cubes est rangé. Un ballon s'immobilise. Adam répète tout bas le geste. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Adam dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8056,6 +8100,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8223,6 +8268,7 @@
           <t>narrateur|Adam se souvient de Léa. Et de les cubes. Et de un morceau de pain. Le vent est doux. Adam serre la main de papa. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Adam dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8390,6 +8436,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8557,6 +8604,7 @@
           <t>narrateur|Léa veut le livre. Elle pointe partout. Cette énergie n'est pas une faute. Adam peut jouer ou attendre. Papa reste tout près. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8748,6 +8796,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8915,6 +8964,7 @@
           <t>narrateur|Avec une pomme. Après le livre. Près de Léa. Adam s'arrête. On range un objet. Adam pose sa tête un moment. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Adam dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9082,6 +9132,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9249,6 +9300,7 @@
           <t>narrateur|Adam range le livre. un yaourt reste près de Léa. On souffle doucement. Adam tend un yaourt à maman. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Adam dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9416,6 +9468,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9583,6 +9636,7 @@
           <t>narrateur|Un morceau de pain est là. le livre aussi. Léa reste dans le souvenir. Une feuille tombe. Adam sourit. Papa sourit aussi. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Adam dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9750,6 +9804,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9917,6 +9972,7 @@
           <t>narrateur|Léa veut la dînette. Elle fait cliqueter. Cette énergie n'est pas une faute. Adam peut jouer ou attendre. Papa montre le geste, lentement. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10108,6 +10164,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10275,6 +10332,7 @@
           <t>narrateur|Adam rejoint une pomme. la dînette est rangé. Léa est fini. Le sol est un peu froid. Maman n'est pas loin. Adam les rejoint. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Adam dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10442,6 +10500,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10609,6 +10668,7 @@
           <t>narrateur|Près de un yaourt. Adam pose la dînette. Léa est derrière. Ça sent le pain chaud. Adam range la tasse. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Adam dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10776,6 +10836,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10943,6 +11004,7 @@
           <t>narrateur|Adam montre un morceau de pain. Papa a vu Léa. Et la dînette. On dit merci. Adam essuie ses mains. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Adam dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11110,6 +11172,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11277,6 +11340,7 @@
           <t>narrateur|Adam rejoint Sami. Sami tourne, puis s'assoit. Il a beaucoup d'énergie. Cette énergie n'est pas une faute. Adam joue un moment, puis attend. Papa reste tout près. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11460,6 +11524,7 @@
           <t>narrateur|On demande à un adulte ?</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11631,6 +11696,7 @@
           <t>narrateur|Oui. Cette énergie n'est pas une faute. On peut jouer ou attendre. Adam hoche la tête. On continue, avec papa. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11822,6 +11888,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11989,6 +12056,7 @@
           <t>narrateur|Sami veut les cubes. Il court les chercher. Cette énergie n'est pas une faute. Adam peut jouer ou attendre. Papa reste tout près. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12180,6 +12248,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12349,6 +12418,7 @@
 narrateur|Adam dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12516,6 +12586,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12683,6 +12754,7 @@
           <t>narrateur|Adam s'arrête près de un yaourt. les cubes est rangé. L'eau coule, tout petit bruit. Adam ferme la porte, tout doux. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Adam dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12850,6 +12922,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13017,6 +13090,7 @@
           <t>narrateur|Adam se souvient de Sami. Et de les cubes. Et de un morceau de pain. La lumière est claire. Adam marche près de papa. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Adam dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13184,6 +13258,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13351,6 +13426,7 @@
           <t>narrateur|Sami veut le livre. Il s'assoit, puis se lève. Cette énergie n'est pas une faute. Adam peut jouer ou attendre. Papa montre le geste, lentement. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13542,6 +13618,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13709,6 +13786,7 @@
           <t>narrateur|Avec une pomme. Après le livre. Près de Sami. Adam s'arrête. Un vélo passe au loin. Adam écoute papa encore une fois. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Adam dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13876,6 +13954,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14043,6 +14122,7 @@
           <t>narrateur|Adam range le livre. un yaourt reste près de Sami. Une chaussette est encore sablée. Adam ferme le sac. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Adam dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14210,6 +14290,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14377,6 +14458,7 @@
           <t>narrateur|Un morceau de pain est là. le livre aussi. Sami reste dans le souvenir. Une tasse cliquette. Adam raccroche un linge. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Adam dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14544,6 +14626,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14712,6 +14795,7 @@
 papa|Je suis là. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14903,6 +14987,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15070,6 +15155,7 @@
           <t>narrateur|Adam rejoint une pomme. la dînette est rangé. Sami est fini. Un panier est posé sur le banc. Adam boit une gorgée d'eau. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Adam dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15237,6 +15323,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15404,6 +15491,7 @@
           <t>narrateur|Près de un yaourt. Adam pose la dînette. Sami est derrière. On attend son tour. Adam prend la main de papa. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Adam dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15571,6 +15659,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15738,6 +15827,7 @@
           <t>narrateur|Adam montre un morceau de pain. Papa a vu Sami. Et la dînette. Un galet est encore chaud. Adam range encore un peu, près de papa. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Adam dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15905,6 +15995,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15923,7 +16014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15947,6 +16038,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -15961,7 +16066,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16148,6 +16253,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/TREE-DIF-006.xlsx
+++ b/stories/arbres/TREE-DIF-006.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -552,7 +552,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Un camarade qui bouge beaucoup — dans le jardin</t>
+          <t>Les gouttes de l'arrosoir</t>
         </is>
       </c>
     </row>
@@ -843,6 +843,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>L'arrosoir goutte sur la dalle. Aniss rejoint Mila dans le jardin. Mila a beaucoup d'énergie. Ce n'est pas une faute. Ils jouent, ou ils attendent.</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1197,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Adam est dans le jardin, avec papa. Maman arrose une fleur. Un camarade court, saute, tourne. Il a beaucoup d'énergie. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut jouer ensemble.</t>
+          <t>Une goutte tombe de l'arrosoir. Elle fait ploc, sur la dalle. L'herbe brille encore, toute mouillée. Ça sent la terre, et la menthe. Un linge rose sèche, tout léger. Papa pose ses bottes près du seau. Tu as vu la goutte, Aniss ? Elle a fait ploc. La dalle est froide, hein ? Oui, papa. Un seau jaune attend près du tuyau. Une abeille passe, tout bas. Le banc de bois est déjà tiède. Le cerisier laisse tomber un pétale. Je verse encore un peu d'eau. L'eau chante dans les fleurs. Tu sens la menthe ? Oui. Elle pique un peu. En ce moment, Aniss s'accroupit. Il touche une feuille, toute douce. Mila arrive dans le jardin. Elle court. Elle saute. Elle tourne. Ses chaussures font toc toc, sur l'herbe. Elle a beaucoup d'énergie. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut demander à un adulte. Elle bouge tout le temps. Ce n'est pas une faute, Aniss. Mila s'arrête. Puis elle reprend. On joue ? On peut jouer ensemble. On peut aussi attendre son tour. Je peux attendre. Bravo, Aniss. C'est du bon travail. Le bac attend, tout sombre. Le cerisier attend, tout rose. Le banc attend, tout calme. Tu es prêt ? Oui, maman.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1325,11 +1337,54 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Adam est dans le jardin, avec papa. Maman arrose une fleur. Un camarade court, saute, tourne. Il a beaucoup d'énergie.
-papa|Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut jouer ensemble.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|Une goutte tombe de l'arrosoir.
+narrateur|Elle fait ploc, sur la dalle.
+narrateur|L'herbe brille encore, toute mouillée.
+narrateur|Ça sent la terre, et la menthe.
+narrateur|Un linge rose sèche, tout léger.
+narrateur|Papa pose ses bottes près du seau.
+maman|Tu as vu la goutte, Aniss ?
+enfant-m|Elle a fait ploc.
+papa|La dalle est froide, hein ?
+enfant-m|Oui, papa.
+narrateur|Un seau jaune attend près du tuyau.
+narrateur|Une abeille passe, tout bas.
+narrateur|Le banc de bois est déjà tiède.
+narrateur|Le cerisier laisse tomber un pétale.
+maman|Je verse encore un peu d'eau.
+narrateur|L'eau chante dans les fleurs.
+papa|Tu sens la menthe ?
+enfant-m|Oui. Elle pique un peu.
+narrateur|En ce moment, Aniss s'accroupit.
+narrateur|Il touche une feuille, toute douce.
+narrateur|Mila arrive dans le jardin.
+narrateur|Elle court. Elle saute. Elle tourne.
+narrateur|Ses chaussures font toc toc, sur l'herbe.
+narrateur|Elle a beaucoup d'énergie.
+papa|Cette énergie n'est pas une faute.
+maman|On peut jouer ou attendre.
+papa|On peut demander à un adulte.
+enfant-m|Elle bouge tout le temps.
+maman|Ce n'est pas une faute, Aniss.
+narrateur|Mila s'arrête. Puis elle reprend.
+enfant-f|On joue ?
+papa|On peut jouer ensemble.
+papa|On peut aussi attendre son tour.
+enfant-m|Je peux attendre.
+papa|Bravo, Aniss.
+maman|C'est du bon travail.
+narrateur|Le bac attend, tout sombre.
+narrateur|Le cerisier attend, tout rose.
+narrateur|Le banc attend, tout calme.
+maman|Tu es prêt ?
+enfant-m|Oui, maman.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1354,7 +1409,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Aniss va où, dans le jardin ? Le bac, le cerisier, ou le banc.</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1522,7 +1577,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|Aniss va où, dans le jardin ?
+papa|Le bac, le cerisier, ou le banc.</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1550,7 +1606,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Adam rejoint Tom. Tom court autour du bac. Il a beaucoup d'énergie. Cette énergie n'est pas une faute. Adam peut jouer ou attendre. Papa est là. Tom s'arrête, puis reprend. On peut jouer ensemble.</t>
+          <t>Aniss va vers le bac. La terre est sombre, encore mouillée. Une marguerite penche, toute légère. Mila court autour du bac. Elle a beaucoup d'énergie. Cette énergie n'est pas une faute. On peut jouer ou attendre. Je peux attendre mon tour. Oui. On joue ensemble aussi. Mila s'arrête. Puis elle reprend. Tu peux demander à un adulte. Maman, on fait quoi ? On joue, ou on attend. Bravo, Aniss. Le seau jaune reste près du bac.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1690,7 +1746,21 @@
       <c r="AV4" s="2" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Adam rejoint Tom. Tom court autour du bac. Il a beaucoup d'énergie. Cette énergie n'est pas une faute. Adam peut jouer ou attendre. Papa est là. Tom s'arrête, puis reprend. On peut jouer ensemble.</t>
+          <t>narrateur|Aniss va vers le bac.
+narrateur|La terre est sombre, encore mouillée.
+narrateur|Une marguerite penche, toute légère.
+narrateur|Mila court autour du bac.
+narrateur|Elle a beaucoup d'énergie.
+papa|Cette énergie n'est pas une faute.
+maman|On peut jouer ou attendre.
+enfant-m|Je peux attendre mon tour.
+papa|Oui. On joue ensemble aussi.
+narrateur|Mila s'arrête. Puis elle reprend.
+maman|Tu peux demander à un adulte.
+enfant-m|Maman, on fait quoi ?
+maman|On joue, ou on attend.
+papa|Bravo, Aniss.
+narrateur|Le seau jaune reste près du bac.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1718,7 +1788,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Beaucoup d'énergie, c'est une faute ?</t>
+          <t>Cette énergie, c'est une faute ?</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1878,7 +1948,7 @@
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Beaucoup d'énergie, c'est une faute ?</t>
+          <t>narrateur|Cette énergie, c'est une faute ?</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1906,7 +1976,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Oui. Cette énergie n'est pas une faute. On peut jouer ou attendre. Adam respire. Papa est là. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut jouer ensemble.</t>
+          <t>Oui. Cette énergie n'est pas une faute. On peut jouer ou attendre. Aniss respire, tout calme. Bravo, Aniss. Tu as fait du bon travail. Merci, papa. On continue, tout doux.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2050,7 +2120,14 @@
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|Oui. Cette énergie n'est pas une faute. On peut jouer ou attendre. Adam respire. Papa est là. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut jouer ensemble.</t>
+          <t>narrateur|Oui.
+papa|Cette énergie n'est pas une faute.
+maman|On peut jouer ou attendre.
+narrateur|Aniss respire, tout calme.
+papa|Bravo, Aniss.
+papa|Tu as fait du bon travail.
+enfant-m|Merci, papa.
+maman|On continue, tout doux.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2078,7 +2155,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre les cubes, le livre, ou la dînette.</t>
+          <t>On prend quel jeu ? Les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -2242,7 +2319,8 @@
       <c r="AV7" s="2" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+          <t>narrateur|On prend quel jeu ?
+maman|Les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr"/>
@@ -2270,7 +2348,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Tom veut les cubes. Il bouge beaucoup. Cette énergie n'est pas une faute. Adam peut jouer ou attendre. Papa montre le geste, lentement. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut jouer ensemble.</t>
+          <t>Près de le bac, Mila veut les cubes. Les cubes sont en bois, un peu rudes. Un cube rouge fait toc, sur l'herbe. Mila bouge beaucoup, encore. Cette énergie n'est pas une faute. On peut jouer ou attendre. J'attends mon tour. Oui. Puis on joue ensemble. Mila pose un cube. Puis elle reprend. Tu peux demander à papa. Papa, c'est mon tour ? Oui. Bravo, Aniss. Le cube rouge reste dans sa main.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -2410,7 +2488,19 @@
       <c r="AV8" s="2" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>narrateur|Tom veut les cubes. Il bouge beaucoup. Cette énergie n'est pas une faute. Adam peut jouer ou attendre. Papa montre le geste, lentement. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut jouer ensemble.</t>
+          <t>narrateur|Près de le bac, Mila veut les cubes.
+narrateur|Les cubes sont en bois, un peu rudes.
+narrateur|Un cube rouge fait toc, sur l'herbe.
+narrateur|Mila bouge beaucoup, encore.
+papa|Cette énergie n'est pas une faute.
+maman|On peut jouer ou attendre.
+enfant-m|J'attends mon tour.
+papa|Oui. Puis on joue ensemble.
+narrateur|Mila pose un cube. Puis elle reprend.
+maman|Tu peux demander à papa.
+enfant-m|Papa, c'est mon tour ?
+papa|Oui. Bravo, Aniss.
+narrateur|Le cube rouge reste dans sa main.</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr"/>
@@ -2438,7 +2528,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+          <t>On prend quel goûter ? Une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -2602,7 +2692,8 @@
       <c r="AV9" s="2" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+          <t>narrateur|On prend quel goûter ?
+papa|Une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr"/>
@@ -2630,7 +2721,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Adam a choisi Tom. Puis les cubes. Puis une pomme. Une pomme brille un peu. Adam dit merci à papa. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Adam dit merci à papa.</t>
+          <t>Une pomme brille au bord du bac. Un cube rouge a une goutte. Aniss a choisi le bac. Puis les cubes. Puis une pomme. Mila a encore de l'énergie. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue ou on attend. On peut demander à un adulte. Merci, papa. Bravo, Aniss. C'est du bon travail. Merci, maman. Le jardin redevient calme, tout doux. Aniss se souvient du bac, et des cubes.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -2770,7 +2861,21 @@
       <c r="AV10" s="2" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>narrateur|Adam a choisi Tom. Puis les cubes. Puis une pomme. Une pomme brille un peu. Adam dit merci à papa. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Adam dit merci à papa.</t>
+          <t>narrateur|Une pomme brille au bord du bac.
+narrateur|Un cube rouge a une goutte.
+narrateur|Aniss a choisi le bac.
+narrateur|Puis les cubes. Puis une pomme.
+narrateur|Mila a encore de l'énergie.
+papa|Cette énergie n'est pas une faute.
+maman|On peut jouer ou attendre.
+enfant-m|On joue ou on attend.
+papa|On peut demander à un adulte.
+enfant-m|Merci, papa.
+maman|Bravo, Aniss.
+maman|C'est du bon travail.
+enfant-f|Merci, maman.
+narrateur|Le jardin redevient calme, tout doux.
+narrateur|Aniss se souvient du bac, et des cubes.</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr"/>
@@ -2798,7 +2903,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Mila a de l'énergie. Ce n'est pas une faute. On a joué ou on a attendu. Bravo, Aniss. Tu as fait du bon travail. Aniss a visité le bac. Il a pris les cubes. Il a goûté une pomme. Une coccinelle s'est posée sur la marguerite. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -2938,7 +3043,16 @@
       <c r="AV11" s="2" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Mila a de l'énergie.
+enfant-m|Ce n'est pas une faute.
+papa|On a joué ou on a attendu.
+maman|Bravo, Aniss.
+papa|Tu as fait du bon travail.
+narrateur|Aniss a visité le bac.
+narrateur|Il a pris les cubes.
+narrateur|Il a goûté une pomme.
+narrateur|Une coccinelle s'est posée sur la marguerite.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr"/>
@@ -2966,7 +3080,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Adam s'arrête près de un yaourt. les cubes est rangé. Les chaussures font toc toc. Adam enfile ses chaussons. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Adam dit merci à papa.</t>
+          <t>Un yaourt frais attend près des cubes. La terre du bac est encore sombre. Aniss a choisi le bac. Puis les cubes. Puis un yaourt. Mila a encore de l'énergie. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue ou on attend. On peut demander à un adulte. Merci, papa. Bravo, Aniss. C'est du bon travail. Merci, maman. Le jardin redevient calme, tout doux. Aniss se souvient du bac, et des cubes.</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -3106,7 +3220,21 @@
       <c r="AV12" s="2" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>narrateur|Adam s'arrête près de un yaourt. les cubes est rangé. Les chaussures font toc toc. Adam enfile ses chaussons. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Adam dit merci à papa.</t>
+          <t>narrateur|Un yaourt frais attend près des cubes.
+narrateur|La terre du bac est encore sombre.
+narrateur|Aniss a choisi le bac.
+narrateur|Puis les cubes. Puis un yaourt.
+narrateur|Mila a encore de l'énergie.
+papa|Cette énergie n'est pas une faute.
+maman|On peut jouer ou attendre.
+enfant-m|On joue ou on attend.
+papa|On peut demander à un adulte.
+enfant-m|Merci, papa.
+maman|Bravo, Aniss.
+maman|C'est du bon travail.
+enfant-f|Merci, maman.
+narrateur|Le jardin redevient calme, tout doux.
+narrateur|Aniss se souvient du bac, et des cubes.</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr"/>
@@ -3134,7 +3262,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Mila a de l'énergie. Ce n'est pas une faute. On a joué ou on a attendu. Bravo, Aniss. Tu as fait du bon travail. Aniss a visité le bac. Il a pris les cubes. Il a goûté un yaourt. La cuillère a gardé un peu de froid. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -3274,7 +3402,16 @@
       <c r="AV13" s="2" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Mila a de l'énergie.
+enfant-m|Ce n'est pas une faute.
+papa|On a joué ou on a attendu.
+maman|Bravo, Aniss.
+papa|Tu as fait du bon travail.
+narrateur|Aniss a visité le bac.
+narrateur|Il a pris les cubes.
+narrateur|Il a goûté un yaourt.
+narrateur|La cuillère a gardé un peu de froid.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr"/>
@@ -3302,7 +3439,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Adam se souvient de Tom. Et de les cubes. Et de un morceau de pain. Une cloche tinte, tout loin. Adam montre un morceau de pain à papa. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Adam dit merci à papa.</t>
+          <t>Un morceau de pain sent le four. Un cube jaune garde une miette. Aniss a choisi le bac. Puis les cubes. Puis un morceau de pain. Mila a encore de l'énergie. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue ou on attend. On peut demander à un adulte. Merci, papa. Bravo, Aniss. C'est du bon travail. Merci, maman. Le jardin redevient calme, tout doux. Aniss se souvient du bac, et des cubes.</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -3442,7 +3579,21 @@
       <c r="AV14" s="2" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>narrateur|Adam se souvient de Tom. Et de les cubes. Et de un morceau de pain. Une cloche tinte, tout loin. Adam montre un morceau de pain à papa. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Adam dit merci à papa.</t>
+          <t>narrateur|Un morceau de pain sent le four.
+narrateur|Un cube jaune garde une miette.
+narrateur|Aniss a choisi le bac.
+narrateur|Puis les cubes. Puis un morceau de pain.
+narrateur|Mila a encore de l'énergie.
+papa|Cette énergie n'est pas une faute.
+maman|On peut jouer ou attendre.
+enfant-m|On joue ou on attend.
+papa|On peut demander à un adulte.
+enfant-m|Merci, papa.
+maman|Bravo, Aniss.
+maman|C'est du bon travail.
+enfant-f|Merci, maman.
+narrateur|Le jardin redevient calme, tout doux.
+narrateur|Aniss se souvient du bac, et des cubes.</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr"/>
@@ -3470,7 +3621,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Mila a de l'énergie. Ce n'est pas une faute. On a joué ou on a attendu. Bravo, Aniss. Tu as fait du bon travail. Aniss a visité le bac. Il a pris les cubes. Il a goûté un morceau de pain. Une miette dort encore sur le bord du bac. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -3610,7 +3761,16 @@
       <c r="AV15" s="2" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Mila a de l'énergie.
+enfant-m|Ce n'est pas une faute.
+papa|On a joué ou on a attendu.
+maman|Bravo, Aniss.
+papa|Tu as fait du bon travail.
+narrateur|Aniss a visité le bac.
+narrateur|Il a pris les cubes.
+narrateur|Il a goûté un morceau de pain.
+narrateur|Une miette dort encore sur le bord du bac.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr"/>
@@ -3638,7 +3798,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Tom veut le livre. Il tourne les pages vite. Cette énergie n'est pas une faute. Adam peut jouer ou attendre. Je suis là. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut jouer ensemble.</t>
+          <t>Près de le bac, Mila veut le livre. La couverture est un peu rêche. Une page chuchote sous le doigt. Mila tourne les pages, tout vite. Cette énergie n'est pas une faute. On peut jouer ou attendre. On attend un peu. Oui. Puis on lit ensemble. Mila souffle. Elle pose le livre. Tu peux demander à maman. Maman, on lit ? Oui. Bravo. Tu as attendu. Un pétale reste sur la page.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -3778,8 +3938,19 @@
       <c r="AV16" s="2" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>narrateur|Tom veut le livre. Il tourne les pages vite. Cette énergie n'est pas une faute. Adam peut jouer ou attendre.
-papa|Je suis là. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut jouer ensemble.</t>
+          <t>narrateur|Près de le bac, Mila veut le livre.
+narrateur|La couverture est un peu rêche.
+narrateur|Une page chuchote sous le doigt.
+narrateur|Mila tourne les pages, tout vite.
+maman|Cette énergie n'est pas une faute.
+papa|On peut jouer ou attendre.
+enfant-m|On attend un peu.
+maman|Oui. Puis on lit ensemble.
+narrateur|Mila souffle. Elle pose le livre.
+papa|Tu peux demander à maman.
+enfant-m|Maman, on lit ?
+maman|Oui. Bravo. Tu as attendu.
+narrateur|Un pétale reste sur la page.</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr"/>
@@ -3807,7 +3978,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+          <t>On prend quel goûter ? Une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -3971,7 +4142,8 @@
       <c r="AV17" s="2" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+          <t>narrateur|On prend quel goûter ?
+papa|Une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr"/>
@@ -3999,7 +4171,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Avec une pomme. Après le livre. Près de Tom. Adam s'arrête. On rit un peu. Adam s'assoit près de papa. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Adam dit merci à papa.</t>
+          <t>Une pomme roule vers le livre. Le bac a laissé une tache d'eau. Aniss a choisi le bac. Puis le livre. Puis une pomme. Mila a encore de l'énergie. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue ou on attend. On peut demander à un adulte. Merci, papa. Bravo, Aniss. C'est du bon travail. Merci, maman. Le jardin redevient calme, tout doux. Aniss se souvient du bac, et du livre.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -4139,7 +4311,21 @@
       <c r="AV18" s="2" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>narrateur|Avec une pomme. Après le livre. Près de Tom. Adam s'arrête. On rit un peu. Adam s'assoit près de papa. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Adam dit merci à papa.</t>
+          <t>narrateur|Une pomme roule vers le livre.
+narrateur|Le bac a laissé une tache d'eau.
+narrateur|Aniss a choisi le bac.
+narrateur|Puis le livre. Puis une pomme.
+narrateur|Mila a encore de l'énergie.
+papa|Cette énergie n'est pas une faute.
+maman|On peut jouer ou attendre.
+enfant-m|On joue ou on attend.
+papa|On peut demander à un adulte.
+enfant-m|Merci, papa.
+maman|Bravo, Aniss.
+maman|C'est du bon travail.
+enfant-f|Merci, maman.
+narrateur|Le jardin redevient calme, tout doux.
+narrateur|Aniss se souvient du bac, et du livre.</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr"/>
@@ -4167,7 +4353,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Mila a de l'énergie. Ce n'est pas une faute. On a joué ou on a attendu. Bravo, Aniss. Tu as fait du bon travail. Aniss a visité le bac. Il a pris le livre. Il a goûté une pomme. Un pétale a séché sur la pomme. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -4307,7 +4493,16 @@
       <c r="AV19" s="2" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Mila a de l'énergie.
+enfant-m|Ce n'est pas une faute.
+papa|On a joué ou on a attendu.
+maman|Bravo, Aniss.
+papa|Tu as fait du bon travail.
+narrateur|Aniss a visité le bac.
+narrateur|Il a pris le livre.
+narrateur|Il a goûté une pomme.
+narrateur|Un pétale a séché sur la pomme.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr"/>
@@ -4335,7 +4530,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Adam range le livre. un yaourt reste près de Tom. Il y a des miettes sur la table. Adam range Tom dans sa tête, comme un souvenir. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Adam dit merci à papa.</t>
+          <t>Un yaourt cliquette près du livre. Une marguerite penche vers la page. Aniss a choisi le bac. Puis le livre. Puis un yaourt. Mila a encore de l'énergie. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue ou on attend. On peut demander à un adulte. Merci, papa. Bravo, Aniss. C'est du bon travail. Merci, maman. Le jardin redevient calme, tout doux. Aniss se souvient du bac, et du livre.</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -4475,7 +4670,21 @@
       <c r="AV20" s="2" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>narrateur|Adam range le livre. un yaourt reste près de Tom. Il y a des miettes sur la table. Adam range Tom dans sa tête, comme un souvenir. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Adam dit merci à papa.</t>
+          <t>narrateur|Un yaourt cliquette près du livre.
+narrateur|Une marguerite penche vers la page.
+narrateur|Aniss a choisi le bac.
+narrateur|Puis le livre. Puis un yaourt.
+narrateur|Mila a encore de l'énergie.
+papa|Cette énergie n'est pas une faute.
+maman|On peut jouer ou attendre.
+enfant-m|On joue ou on attend.
+papa|On peut demander à un adulte.
+enfant-m|Merci, papa.
+maman|Bravo, Aniss.
+maman|C'est du bon travail.
+enfant-f|Merci, maman.
+narrateur|Le jardin redevient calme, tout doux.
+narrateur|Aniss se souvient du bac, et du livre.</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr"/>
@@ -4503,7 +4712,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Mila a de l'énergie. Ce n'est pas une faute. On a joué ou on a attendu. Bravo, Aniss. Tu as fait du bon travail. Aniss a visité le bac. Il a pris le livre. Il a goûté un yaourt. Le livre a une petite tache d'eau. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -4643,7 +4852,16 @@
       <c r="AV21" s="2" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Mila a de l'énergie.
+enfant-m|Ce n'est pas une faute.
+papa|On a joué ou on a attendu.
+maman|Bravo, Aniss.
+papa|Tu as fait du bon travail.
+narrateur|Aniss a visité le bac.
+narrateur|Il a pris le livre.
+narrateur|Il a goûté un yaourt.
+narrateur|Le livre a une petite tache d'eau.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr"/>
@@ -4671,7 +4889,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Un morceau de pain est là. le livre aussi. Tom reste dans le souvenir. La couverture est douce. Adam pose le livre à sa place. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Adam dit merci à papa.</t>
+          <t>Un morceau de pain repose sur le livre. L'eau du bac chante encore. Aniss a choisi le bac. Puis le livre. Puis un morceau de pain. Mila a encore de l'énergie. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue ou on attend. On peut demander à un adulte. Merci, papa. Bravo, Aniss. C'est du bon travail. Merci, maman. Le jardin redevient calme, tout doux. Aniss se souvient du bac, et du livre.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -4811,7 +5029,21 @@
       <c r="AV22" s="2" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>narrateur|Un morceau de pain est là. le livre aussi. Tom reste dans le souvenir. La couverture est douce. Adam pose le livre à sa place. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Adam dit merci à papa.</t>
+          <t>narrateur|Un morceau de pain repose sur le livre.
+narrateur|L'eau du bac chante encore.
+narrateur|Aniss a choisi le bac.
+narrateur|Puis le livre. Puis un morceau de pain.
+narrateur|Mila a encore de l'énergie.
+papa|Cette énergie n'est pas une faute.
+maman|On peut jouer ou attendre.
+enfant-m|On joue ou on attend.
+papa|On peut demander à un adulte.
+enfant-m|Merci, papa.
+maman|Bravo, Aniss.
+maman|C'est du bon travail.
+enfant-f|Merci, maman.
+narrateur|Le jardin redevient calme, tout doux.
+narrateur|Aniss se souvient du bac, et du livre.</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr"/>
@@ -4839,7 +5071,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Mila a de l'énergie. Ce n'est pas une faute. On a joué ou on a attendu. Bravo, Aniss. Tu as fait du bon travail. Aniss a visité le bac. Il a pris le livre. Il a goûté un morceau de pain. Le pain a tiédi près des fleurs. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -4979,7 +5211,16 @@
       <c r="AV23" s="2" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Mila a de l'énergie.
+enfant-m|Ce n'est pas une faute.
+papa|On a joué ou on a attendu.
+maman|Bravo, Aniss.
+papa|Tu as fait du bon travail.
+narrateur|Aniss a visité le bac.
+narrateur|Il a pris le livre.
+narrateur|Il a goûté un morceau de pain.
+narrateur|Le pain a tiédi près des fleurs.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr"/>
@@ -5007,7 +5248,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Tom veut la dînette. Il range et dérange. Cette énergie n'est pas une faute. Adam peut jouer ou attendre. Papa reste tout près. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut jouer ensemble.</t>
+          <t>Près de le bac, Mila veut la dînette. Une petite tasse sonne, tout creux. Ça sent presque la soupe, pour de rire. Mila range. Puis elle dérange. Cette énergie n'est pas une faute. On peut jouer ou attendre. On sert à tour de rôle. Oui. On attend son tour. Mila pose la cuillère, tout doux. Tu as demandé. C'est bien. Merci, maman. Bravo, vous deux. La petite casserole reste au calme.</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -5147,7 +5388,19 @@
       <c r="AV24" s="2" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>narrateur|Tom veut la dînette. Il range et dérange. Cette énergie n'est pas une faute. Adam peut jouer ou attendre. Papa reste tout près. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut jouer ensemble.</t>
+          <t>narrateur|Près de le bac, Mila veut la dînette.
+narrateur|Une petite tasse sonne, tout creux.
+narrateur|Ça sent presque la soupe, pour de rire.
+narrateur|Mila range. Puis elle dérange.
+papa|Cette énergie n'est pas une faute.
+maman|On peut jouer ou attendre.
+enfant-m|On sert à tour de rôle.
+papa|Oui. On attend son tour.
+narrateur|Mila pose la cuillère, tout doux.
+maman|Tu as demandé. C'est bien.
+enfant-m|Merci, maman.
+papa|Bravo, vous deux.
+narrateur|La petite casserole reste au calme.</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr"/>
@@ -5175,7 +5428,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+          <t>On prend quel goûter ? Une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -5339,7 +5592,8 @@
       <c r="AV25" s="2" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+          <t>narrateur|On prend quel goûter ?
+papa|Une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr"/>
@@ -5367,7 +5621,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Adam rejoint une pomme. la dînette est rangé. Tom est fini. On se tient la main. Adam chuchote : c'est fini. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Adam dit merci à papa.</t>
+          <t>Une pomme sert de gâteau, pour de rire. La dînette est près du bac. Aniss a choisi le bac. Puis la dînette. Puis une pomme. Mila a encore de l'énergie. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue ou on attend. On peut demander à un adulte. Merci, papa. Bravo, Aniss. C'est du bon travail. Merci, maman. Le jardin redevient calme, tout doux. Aniss se souvient du bac, et de la dînette.</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -5507,7 +5761,21 @@
       <c r="AV26" s="2" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>narrateur|Adam rejoint une pomme. la dînette est rangé. Tom est fini. On se tient la main. Adam chuchote : c'est fini. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Adam dit merci à papa.</t>
+          <t>narrateur|Une pomme sert de gâteau, pour de rire.
+narrateur|La dînette est près du bac.
+narrateur|Aniss a choisi le bac.
+narrateur|Puis la dînette. Puis une pomme.
+narrateur|Mila a encore de l'énergie.
+papa|Cette énergie n'est pas une faute.
+maman|On peut jouer ou attendre.
+enfant-m|On joue ou on attend.
+papa|On peut demander à un adulte.
+enfant-m|Merci, papa.
+maman|Bravo, Aniss.
+maman|C'est du bon travail.
+enfant-f|Merci, maman.
+narrateur|Le jardin redevient calme, tout doux.
+narrateur|Aniss se souvient du bac, et de la dînette.</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr"/>
@@ -5535,7 +5803,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Mila a de l'énergie. Ce n'est pas une faute. On a joué ou on a attendu. Bravo, Aniss. Tu as fait du bon travail. Aniss a visité le bac. Il a pris la dînette. Il a goûté une pomme. La petite tasse a un rond de pomme. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -5675,7 +5943,16 @@
       <c r="AV27" s="2" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Mila a de l'énergie.
+enfant-m|Ce n'est pas une faute.
+papa|On a joué ou on a attendu.
+maman|Bravo, Aniss.
+papa|Tu as fait du bon travail.
+narrateur|Aniss a visité le bac.
+narrateur|Il a pris la dînette.
+narrateur|Il a goûté une pomme.
+narrateur|La petite tasse a un rond de pomme.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr"/>
@@ -5703,7 +5980,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Près de un yaourt. Adam pose la dînette. Tom est derrière. Un chat miaule une fois. Adam souffle, puis sourit à papa. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Adam dit merci à papa.</t>
+          <t>Un yaourt brille comme de la crème. La petite tasse a une goutte. Aniss a choisi le bac. Puis la dînette. Puis un yaourt. Mila a encore de l'énergie. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue ou on attend. On peut demander à un adulte. Merci, papa. Bravo, Aniss. C'est du bon travail. Merci, maman. Le jardin redevient calme, tout doux. Aniss se souvient du bac, et de la dînette.</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -5843,7 +6120,21 @@
       <c r="AV28" s="2" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>narrateur|Près de un yaourt. Adam pose la dînette. Tom est derrière. Un chat miaule une fois. Adam souffle, puis sourit à papa. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Adam dit merci à papa.</t>
+          <t>narrateur|Un yaourt brille comme de la crème.
+narrateur|La petite tasse a une goutte.
+narrateur|Aniss a choisi le bac.
+narrateur|Puis la dînette. Puis un yaourt.
+narrateur|Mila a encore de l'énergie.
+papa|Cette énergie n'est pas une faute.
+maman|On peut jouer ou attendre.
+enfant-m|On joue ou on attend.
+papa|On peut demander à un adulte.
+enfant-m|Merci, papa.
+maman|Bravo, Aniss.
+maman|C'est du bon travail.
+enfant-f|Merci, maman.
+narrateur|Le jardin redevient calme, tout doux.
+narrateur|Aniss se souvient du bac, et de la dînette.</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr"/>
@@ -5871,7 +6162,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Mila a de l'énergie. Ce n'est pas une faute. On a joué ou on a attendu. Bravo, Aniss. Tu as fait du bon travail. Aniss a visité le bac. Il a pris la dînette. Il a goûté un yaourt. La casserole de dînette s'est tue. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -6011,7 +6302,16 @@
       <c r="AV29" s="2" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Mila a de l'énergie.
+enfant-m|Ce n'est pas une faute.
+papa|On a joué ou on a attendu.
+maman|Bravo, Aniss.
+papa|Tu as fait du bon travail.
+narrateur|Aniss a visité le bac.
+narrateur|Il a pris la dînette.
+narrateur|Il a goûté un yaourt.
+narrateur|La casserole de dînette s'est tue.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr"/>
@@ -6039,7 +6339,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Adam montre un morceau de pain. Papa a vu Tom. Et la dînette. Un linge sèche à l'air. Adam caresse le doudou. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Adam dit merci à papa.</t>
+          <t>Un morceau de pain devient un gâteau. La dînette a des miettes de terre. Aniss a choisi le bac. Puis la dînette. Puis un morceau de pain. Mila a encore de l'énergie. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue ou on attend. On peut demander à un adulte. Merci, papa. Bravo, Aniss. C'est du bon travail. Merci, maman. Le jardin redevient calme, tout doux. Aniss se souvient du bac, et de la dînette.</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -6179,7 +6479,21 @@
       <c r="AV30" s="2" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>narrateur|Adam montre un morceau de pain. Papa a vu Tom. Et la dînette. Un linge sèche à l'air. Adam caresse le doudou. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Adam dit merci à papa.</t>
+          <t>narrateur|Un morceau de pain devient un gâteau.
+narrateur|La dînette a des miettes de terre.
+narrateur|Aniss a choisi le bac.
+narrateur|Puis la dînette. Puis un morceau de pain.
+narrateur|Mila a encore de l'énergie.
+papa|Cette énergie n'est pas une faute.
+maman|On peut jouer ou attendre.
+enfant-m|On joue ou on attend.
+papa|On peut demander à un adulte.
+enfant-m|Merci, papa.
+maman|Bravo, Aniss.
+maman|C'est du bon travail.
+enfant-f|Merci, maman.
+narrateur|Le jardin redevient calme, tout doux.
+narrateur|Aniss se souvient du bac, et de la dînette.</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr"/>
@@ -6207,7 +6521,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Mila a de l'énergie. Ce n'est pas une faute. On a joué ou on a attendu. Bravo, Aniss. Tu as fait du bon travail. Aniss a visité le bac. Il a pris la dînette. Il a goûté un morceau de pain. Une miette reste dans la petite assiette. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -6347,7 +6661,16 @@
       <c r="AV31" s="2" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Mila a de l'énergie.
+enfant-m|Ce n'est pas une faute.
+papa|On a joué ou on a attendu.
+maman|Bravo, Aniss.
+papa|Tu as fait du bon travail.
+narrateur|Aniss a visité le bac.
+narrateur|Il a pris la dînette.
+narrateur|Il a goûté un morceau de pain.
+narrateur|Une miette reste dans la petite assiette.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr"/>
@@ -6375,7 +6698,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Adam rejoint Léa. Léa saute sur place. Elle a beaucoup d'énergie. Cette énergie n'est pas une faute. Adam peut jouer ou attendre. On peut demander à un adulte. On peut jouer ensemble.</t>
+          <t>Aniss va vers le cerisier. Un pétale rose tombe sur l'herbe. L'ombre est douce, un peu froide. Mila saute sous les branches. Elle a beaucoup d'énergie. Cette énergie n'est pas une faute. On peut jouer ou attendre. Je saute, moi. J'attends un peu. C'est bien. On attend son tour. Mila souffle. Puis elle reprend. On peut demander à un adulte. Papa, on joue ensemble ? Oui. On peut aussi attendre. Un pétale reste sur l'épaule d'Aniss.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6515,8 +6838,21 @@
       <c r="AV32" s="2" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>narrateur|Adam rejoint Léa. Léa saute sur place. Elle a beaucoup d'énergie. Cette énergie n'est pas une faute. Adam peut jouer ou attendre.
-maman|On peut demander à un adulte. On peut jouer ensemble.</t>
+          <t>narrateur|Aniss va vers le cerisier.
+narrateur|Un pétale rose tombe sur l'herbe.
+narrateur|L'ombre est douce, un peu froide.
+narrateur|Mila saute sous les branches.
+narrateur|Elle a beaucoup d'énergie.
+maman|Cette énergie n'est pas une faute.
+papa|On peut jouer ou attendre.
+enfant-f|Je saute, moi.
+enfant-m|J'attends un peu.
+papa|C'est bien. On attend son tour.
+narrateur|Mila souffle. Puis elle reprend.
+maman|On peut demander à un adulte.
+enfant-m|Papa, on joue ensemble ?
+papa|Oui. On peut aussi attendre.
+narrateur|Un pétale reste sur l'épaule d'Aniss.</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr"/>
@@ -6728,7 +7064,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Oui. Cette énergie n'est pas une faute. On peut jouer ou attendre. Adam retient le geste. Papa sourit. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut jouer ensemble.</t>
+          <t>Oui. On joue, ou on attend. Cette énergie n'est pas une faute. Aniss retient un petit saut. Bravo. Tu as attendu ton tour. Je peux jouer aussi. Oui. On joue ensemble. On peut aussi attendre.</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -6872,7 +7208,15 @@
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>narrateur|Oui. Cette énergie n'est pas une faute. On peut jouer ou attendre. Adam retient le geste. Papa sourit. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut jouer ensemble.</t>
+          <t>narrateur|Oui.
+maman|On joue, ou on attend.
+papa|Cette énergie n'est pas une faute.
+narrateur|Aniss retient un petit saut.
+maman|Bravo.
+maman|Tu as attendu ton tour.
+enfant-m|Je peux jouer aussi.
+papa|Oui. On joue ensemble.
+papa|On peut aussi attendre.</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr"/>
@@ -6900,7 +7244,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre les cubes, le livre, ou la dînette.</t>
+          <t>On prend quel jeu ? Les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -7064,7 +7408,8 @@
       <c r="AV35" s="2" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+          <t>narrateur|On prend quel jeu ?
+maman|Les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr"/>
@@ -7092,7 +7437,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Léa veut les cubes. Elle saute. Cette énergie n'est pas une faute. Adam peut jouer ou attendre. Je suis là. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut jouer ensemble.</t>
+          <t>Près de le cerisier, Mila veut les cubes. Les cubes sont en bois, un peu rudes. Un cube rouge fait toc, sur l'herbe. Mila bouge beaucoup, encore. Cette énergie n'est pas une faute. On peut jouer ou attendre. J'attends mon tour. Oui. Puis on joue ensemble. Mila pose un cube. Puis elle reprend. Tu peux demander à papa. Papa, c'est mon tour ? Oui. Bravo, Aniss. Le cube rouge reste dans sa main.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -7232,8 +7577,19 @@
       <c r="AV36" s="2" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>narrateur|Léa veut les cubes. Elle saute. Cette énergie n'est pas une faute. Adam peut jouer ou attendre.
-papa|Je suis là. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut jouer ensemble.</t>
+          <t>narrateur|Près de le cerisier, Mila veut les cubes.
+narrateur|Les cubes sont en bois, un peu rudes.
+narrateur|Un cube rouge fait toc, sur l'herbe.
+narrateur|Mila bouge beaucoup, encore.
+papa|Cette énergie n'est pas une faute.
+maman|On peut jouer ou attendre.
+enfant-m|J'attends mon tour.
+papa|Oui. Puis on joue ensemble.
+narrateur|Mila pose un cube. Puis elle reprend.
+maman|Tu peux demander à papa.
+enfant-m|Papa, c'est mon tour ?
+papa|Oui. Bravo, Aniss.
+narrateur|Le cube rouge reste dans sa main.</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr"/>
@@ -7261,7 +7617,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+          <t>On prend quel goûter ? Une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -7425,7 +7781,8 @@
       <c r="AV37" s="2" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+          <t>narrateur|On prend quel goûter ?
+papa|Une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr"/>
@@ -7453,7 +7810,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Adam a choisi Léa. Puis les cubes. Puis une pomme. Un ruban reste dans la poche. Adam plie un pull. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Adam dit merci à papa.</t>
+          <t>Une pomme attrape un pétale rose. Un cube rouge dort sous le cerisier. Aniss a choisi le cerisier. Puis les cubes. Puis une pomme. Mila a encore de l'énergie. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue ou on attend. On peut demander à un adulte. Merci, papa. Bravo, Aniss. C'est du bon travail. Merci, maman. Le jardin redevient calme, tout doux. Aniss se souvient du cerisier, et des cubes.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -7593,7 +7950,21 @@
       <c r="AV38" s="2" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>narrateur|Adam a choisi Léa. Puis les cubes. Puis une pomme. Un ruban reste dans la poche. Adam plie un pull. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Adam dit merci à papa.</t>
+          <t>narrateur|Une pomme attrape un pétale rose.
+narrateur|Un cube rouge dort sous le cerisier.
+narrateur|Aniss a choisi le cerisier.
+narrateur|Puis les cubes. Puis une pomme.
+narrateur|Mila a encore de l'énergie.
+papa|Cette énergie n'est pas une faute.
+maman|On peut jouer ou attendre.
+enfant-m|On joue ou on attend.
+papa|On peut demander à un adulte.
+enfant-m|Merci, papa.
+maman|Bravo, Aniss.
+maman|C'est du bon travail.
+enfant-f|Merci, maman.
+narrateur|Le jardin redevient calme, tout doux.
+narrateur|Aniss se souvient du cerisier, et des cubes.</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr"/>
@@ -7621,7 +7992,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Mila a de l'énergie. Ce n'est pas une faute. On a joué ou on a attendu. Bravo, Aniss. Tu as fait du bon travail. Aniss a visité le cerisier. Il a pris les cubes. Il a goûté une pomme. Un cube rouge a gardé un pétale. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -7761,7 +8132,16 @@
       <c r="AV39" s="2" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Mila a de l'énergie.
+enfant-m|Ce n'est pas une faute.
+papa|On a joué ou on a attendu.
+maman|Bravo, Aniss.
+papa|Tu as fait du bon travail.
+narrateur|Aniss a visité le cerisier.
+narrateur|Il a pris les cubes.
+narrateur|Il a goûté une pomme.
+narrateur|Un cube rouge a gardé un pétale.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr"/>
@@ -7789,7 +8169,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Adam s'arrête près de un yaourt. les cubes est rangé. Un ballon s'immobilise. Adam répète tout bas le geste. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Adam dit merci à papa.</t>
+          <t>Un yaourt est froid, sous l'ombre. Les cubes ont des pétales dessus. Aniss a choisi le cerisier. Puis les cubes. Puis un yaourt. Mila a encore de l'énergie. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue ou on attend. On peut demander à un adulte. Merci, papa. Bravo, Aniss. C'est du bon travail. Merci, maman. Le jardin redevient calme, tout doux. Aniss se souvient du cerisier, et des cubes.</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -7929,7 +8309,21 @@
       <c r="AV40" s="2" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>narrateur|Adam s'arrête près de un yaourt. les cubes est rangé. Un ballon s'immobilise. Adam répète tout bas le geste. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Adam dit merci à papa.</t>
+          <t>narrateur|Un yaourt est froid, sous l'ombre.
+narrateur|Les cubes ont des pétales dessus.
+narrateur|Aniss a choisi le cerisier.
+narrateur|Puis les cubes. Puis un yaourt.
+narrateur|Mila a encore de l'énergie.
+papa|Cette énergie n'est pas une faute.
+maman|On peut jouer ou attendre.
+enfant-m|On joue ou on attend.
+papa|On peut demander à un adulte.
+enfant-m|Merci, papa.
+maman|Bravo, Aniss.
+maman|C'est du bon travail.
+enfant-f|Merci, maman.
+narrateur|Le jardin redevient calme, tout doux.
+narrateur|Aniss se souvient du cerisier, et des cubes.</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr"/>
@@ -7957,7 +8351,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Mila a de l'énergie. Ce n'est pas une faute. On a joué ou on a attendu. Bravo, Aniss. Tu as fait du bon travail. Aniss a visité le cerisier. Il a pris les cubes. Il a goûté un yaourt. L'ombre du cerisier a glissé, tout doux. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -8097,7 +8491,16 @@
       <c r="AV41" s="2" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Mila a de l'énergie.
+enfant-m|Ce n'est pas une faute.
+papa|On a joué ou on a attendu.
+maman|Bravo, Aniss.
+papa|Tu as fait du bon travail.
+narrateur|Aniss a visité le cerisier.
+narrateur|Il a pris les cubes.
+narrateur|Il a goûté un yaourt.
+narrateur|L'ombre du cerisier a glissé, tout doux.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr"/>
@@ -8125,7 +8528,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Adam se souvient de Léa. Et de les cubes. Et de un morceau de pain. Le vent est doux. Adam serre la main de papa. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Adam dit merci à papa.</t>
+          <t>Un morceau de pain a un pétale. Un cube bleu reste dans l'herbe. Aniss a choisi le cerisier. Puis les cubes. Puis un morceau de pain. Mila a encore de l'énergie. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue ou on attend. On peut demander à un adulte. Merci, papa. Bravo, Aniss. C'est du bon travail. Merci, maman. Le jardin redevient calme, tout doux. Aniss se souvient du cerisier, et des cubes.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -8265,7 +8668,21 @@
       <c r="AV42" s="2" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>narrateur|Adam se souvient de Léa. Et de les cubes. Et de un morceau de pain. Le vent est doux. Adam serre la main de papa. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Adam dit merci à papa.</t>
+          <t>narrateur|Un morceau de pain a un pétale.
+narrateur|Un cube bleu reste dans l'herbe.
+narrateur|Aniss a choisi le cerisier.
+narrateur|Puis les cubes. Puis un morceau de pain.
+narrateur|Mila a encore de l'énergie.
+papa|Cette énergie n'est pas une faute.
+maman|On peut jouer ou attendre.
+enfant-m|On joue ou on attend.
+papa|On peut demander à un adulte.
+enfant-m|Merci, papa.
+maman|Bravo, Aniss.
+maman|C'est du bon travail.
+enfant-f|Merci, maman.
+narrateur|Le jardin redevient calme, tout doux.
+narrateur|Aniss se souvient du cerisier, et des cubes.</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr"/>
@@ -8293,7 +8710,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Mila a de l'énergie. Ce n'est pas une faute. On a joué ou on a attendu. Bravo, Aniss. Tu as fait du bon travail. Aniss a visité le cerisier. Il a pris les cubes. Il a goûté un morceau de pain. Une abeille a visité le pain, de loin. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -8433,7 +8850,16 @@
       <c r="AV43" s="2" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Mila a de l'énergie.
+enfant-m|Ce n'est pas une faute.
+papa|On a joué ou on a attendu.
+maman|Bravo, Aniss.
+papa|Tu as fait du bon travail.
+narrateur|Aniss a visité le cerisier.
+narrateur|Il a pris les cubes.
+narrateur|Il a goûté un morceau de pain.
+narrateur|Une abeille a visité le pain, de loin.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr"/>
@@ -8461,7 +8887,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Léa veut le livre. Elle pointe partout. Cette énergie n'est pas une faute. Adam peut jouer ou attendre. Papa reste tout près. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut jouer ensemble.</t>
+          <t>Près de le cerisier, Mila veut le livre. La couverture est un peu rêche. Une page chuchote sous le doigt. Mila tourne les pages, tout vite. Cette énergie n'est pas une faute. On peut jouer ou attendre. On attend un peu. Oui. Puis on lit ensemble. Mila souffle. Elle pose le livre. Tu peux demander à maman. Maman, on lit ? Oui. Bravo. Tu as attendu. Un pétale reste sur la page.</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -8601,7 +9027,19 @@
       <c r="AV44" s="2" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>narrateur|Léa veut le livre. Elle pointe partout. Cette énergie n'est pas une faute. Adam peut jouer ou attendre. Papa reste tout près. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut jouer ensemble.</t>
+          <t>narrateur|Près de le cerisier, Mila veut le livre.
+narrateur|La couverture est un peu rêche.
+narrateur|Une page chuchote sous le doigt.
+narrateur|Mila tourne les pages, tout vite.
+maman|Cette énergie n'est pas une faute.
+papa|On peut jouer ou attendre.
+enfant-m|On attend un peu.
+maman|Oui. Puis on lit ensemble.
+narrateur|Mila souffle. Elle pose le livre.
+papa|Tu peux demander à maman.
+enfant-m|Maman, on lit ?
+maman|Oui. Bravo. Tu as attendu.
+narrateur|Un pétale reste sur la page.</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr"/>
@@ -8629,7 +9067,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+          <t>On prend quel goûter ? Une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -8793,7 +9231,8 @@
       <c r="AV45" s="2" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+          <t>narrateur|On prend quel goûter ?
+papa|Une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr"/>
@@ -8821,7 +9260,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Avec une pomme. Après le livre. Près de Léa. Adam s'arrête. On range un objet. Adam pose sa tête un moment. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Adam dit merci à papa.</t>
+          <t>Une pomme pose sur le livre ouvert. Le cerisier fait une ombre ronde. Aniss a choisi le cerisier. Puis le livre. Puis une pomme. Mila a encore de l'énergie. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue ou on attend. On peut demander à un adulte. Merci, papa. Bravo, Aniss. C'est du bon travail. Merci, maman. Le jardin redevient calme, tout doux. Aniss se souvient du cerisier, et du livre.</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -8961,7 +9400,21 @@
       <c r="AV46" s="2" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>narrateur|Avec une pomme. Après le livre. Près de Léa. Adam s'arrête. On range un objet. Adam pose sa tête un moment. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Adam dit merci à papa.</t>
+          <t>narrateur|Une pomme pose sur le livre ouvert.
+narrateur|Le cerisier fait une ombre ronde.
+narrateur|Aniss a choisi le cerisier.
+narrateur|Puis le livre. Puis une pomme.
+narrateur|Mila a encore de l'énergie.
+papa|Cette énergie n'est pas une faute.
+maman|On peut jouer ou attendre.
+enfant-m|On joue ou on attend.
+papa|On peut demander à un adulte.
+enfant-m|Merci, papa.
+maman|Bravo, Aniss.
+maman|C'est du bon travail.
+enfant-f|Merci, maman.
+narrateur|Le jardin redevient calme, tout doux.
+narrateur|Aniss se souvient du cerisier, et du livre.</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr"/>
@@ -8989,7 +9442,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Mila a de l'énergie. Ce n'est pas une faute. On a joué ou on a attendu. Bravo, Aniss. Tu as fait du bon travail. Aniss a visité le cerisier. Il a pris le livre. Il a goûté une pomme. La page a gardé une odeur de pomme. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -9129,7 +9582,16 @@
       <c r="AV47" s="2" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Mila a de l'énergie.
+enfant-m|Ce n'est pas une faute.
+papa|On a joué ou on a attendu.
+maman|Bravo, Aniss.
+papa|Tu as fait du bon travail.
+narrateur|Aniss a visité le cerisier.
+narrateur|Il a pris le livre.
+narrateur|Il a goûté une pomme.
+narrateur|La page a gardé une odeur de pomme.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr"/>
@@ -9157,7 +9619,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Adam range le livre. un yaourt reste près de Léa. On souffle doucement. Adam tend un yaourt à maman. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Adam dit merci à papa.</t>
+          <t>Un yaourt attend près de la page. Un pétale colle à la couverture. Aniss a choisi le cerisier. Puis le livre. Puis un yaourt. Mila a encore de l'énergie. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue ou on attend. On peut demander à un adulte. Merci, papa. Bravo, Aniss. C'est du bon travail. Merci, maman. Le jardin redevient calme, tout doux. Aniss se souvient du cerisier, et du livre.</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -9297,7 +9759,21 @@
       <c r="AV48" s="2" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>narrateur|Adam range le livre. un yaourt reste près de Léa. On souffle doucement. Adam tend un yaourt à maman. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Adam dit merci à papa.</t>
+          <t>narrateur|Un yaourt attend près de la page.
+narrateur|Un pétale colle à la couverture.
+narrateur|Aniss a choisi le cerisier.
+narrateur|Puis le livre. Puis un yaourt.
+narrateur|Mila a encore de l'énergie.
+papa|Cette énergie n'est pas une faute.
+maman|On peut jouer ou attendre.
+enfant-m|On joue ou on attend.
+papa|On peut demander à un adulte.
+enfant-m|Merci, papa.
+maman|Bravo, Aniss.
+maman|C'est du bon travail.
+enfant-f|Merci, maman.
+narrateur|Le jardin redevient calme, tout doux.
+narrateur|Aniss se souvient du cerisier, et du livre.</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr"/>
@@ -9325,7 +9801,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Mila a de l'énergie. Ce n'est pas une faute. On a joué ou on a attendu. Bravo, Aniss. Tu as fait du bon travail. Aniss a visité le cerisier. Il a pris le livre. Il a goûté un yaourt. Un pétale rose reste dans le livre. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -9465,7 +9941,16 @@
       <c r="AV49" s="2" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Mila a de l'énergie.
+enfant-m|Ce n'est pas une faute.
+papa|On a joué ou on a attendu.
+maman|Bravo, Aniss.
+papa|Tu as fait du bon travail.
+narrateur|Aniss a visité le cerisier.
+narrateur|Il a pris le livre.
+narrateur|Il a goûté un yaourt.
+narrateur|Un pétale rose reste dans le livre.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr"/>
@@ -9493,7 +9978,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Un morceau de pain est là. le livre aussi. Léa reste dans le souvenir. Une feuille tombe. Adam sourit. Papa sourit aussi. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Adam dit merci à papa.</t>
+          <t>Un morceau de pain tiédit au soleil. Le livre garde une page ouverte. Aniss a choisi le cerisier. Puis le livre. Puis un morceau de pain. Mila a encore de l'énergie. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue ou on attend. On peut demander à un adulte. Merci, papa. Bravo, Aniss. C'est du bon travail. Merci, maman. Le jardin redevient calme, tout doux. Aniss se souvient du cerisier, et du livre.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -9633,7 +10118,21 @@
       <c r="AV50" s="2" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>narrateur|Un morceau de pain est là. le livre aussi. Léa reste dans le souvenir. Une feuille tombe. Adam sourit. Papa sourit aussi. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Adam dit merci à papa.</t>
+          <t>narrateur|Un morceau de pain tiédit au soleil.
+narrateur|Le livre garde une page ouverte.
+narrateur|Aniss a choisi le cerisier.
+narrateur|Puis le livre. Puis un morceau de pain.
+narrateur|Mila a encore de l'énergie.
+papa|Cette énergie n'est pas une faute.
+maman|On peut jouer ou attendre.
+enfant-m|On joue ou on attend.
+papa|On peut demander à un adulte.
+enfant-m|Merci, papa.
+maman|Bravo, Aniss.
+maman|C'est du bon travail.
+enfant-f|Merci, maman.
+narrateur|Le jardin redevient calme, tout doux.
+narrateur|Aniss se souvient du cerisier, et du livre.</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr"/>
@@ -9661,7 +10160,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Mila a de l'énergie. Ce n'est pas une faute. On a joué ou on a attendu. Bravo, Aniss. Tu as fait du bon travail. Aniss a visité le cerisier. Il a pris le livre. Il a goûté un morceau de pain. Le cerisier a fait un tapis de pétales. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -9801,7 +10300,16 @@
       <c r="AV51" s="2" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Mila a de l'énergie.
+enfant-m|Ce n'est pas une faute.
+papa|On a joué ou on a attendu.
+maman|Bravo, Aniss.
+papa|Tu as fait du bon travail.
+narrateur|Aniss a visité le cerisier.
+narrateur|Il a pris le livre.
+narrateur|Il a goûté un morceau de pain.
+narrateur|Le cerisier a fait un tapis de pétales.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr"/>
@@ -9829,7 +10337,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Léa veut la dînette. Elle fait cliqueter. Cette énergie n'est pas une faute. Adam peut jouer ou attendre. Papa montre le geste, lentement. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut jouer ensemble.</t>
+          <t>Près de le cerisier, Mila veut la dînette. Une petite tasse sonne, tout creux. Ça sent presque la soupe, pour de rire. Mila range. Puis elle dérange. Cette énergie n'est pas une faute. On peut jouer ou attendre. On sert à tour de rôle. Oui. On attend son tour. Mila pose la cuillère, tout doux. Tu as demandé. C'est bien. Merci, maman. Bravo, vous deux. La petite casserole reste au calme.</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -9969,7 +10477,19 @@
       <c r="AV52" s="2" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>narrateur|Léa veut la dînette. Elle fait cliqueter. Cette énergie n'est pas une faute. Adam peut jouer ou attendre. Papa montre le geste, lentement. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut jouer ensemble.</t>
+          <t>narrateur|Près de le cerisier, Mila veut la dînette.
+narrateur|Une petite tasse sonne, tout creux.
+narrateur|Ça sent presque la soupe, pour de rire.
+narrateur|Mila range. Puis elle dérange.
+papa|Cette énergie n'est pas une faute.
+maman|On peut jouer ou attendre.
+enfant-m|On sert à tour de rôle.
+papa|Oui. On attend son tour.
+narrateur|Mila pose la cuillère, tout doux.
+maman|Tu as demandé. C'est bien.
+enfant-m|Merci, maman.
+papa|Bravo, vous deux.
+narrateur|La petite casserole reste au calme.</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr"/>
@@ -9997,7 +10517,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+          <t>On prend quel goûter ? Une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -10161,7 +10681,8 @@
       <c r="AV53" s="2" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+          <t>narrateur|On prend quel goûter ?
+papa|Une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr"/>
@@ -10189,7 +10710,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Adam rejoint une pomme. la dînette est rangé. Léa est fini. Le sol est un peu froid. Maman n'est pas loin. Adam les rejoint. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Adam dit merci à papa.</t>
+          <t>Une pomme rentre dans une petite assiette. Le cerisier laisse tomber un pétale. Aniss a choisi le cerisier. Puis la dînette. Puis une pomme. Mila a encore de l'énergie. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue ou on attend. On peut demander à un adulte. Merci, papa. Bravo, Aniss. C'est du bon travail. Merci, maman. Le jardin redevient calme, tout doux. Aniss se souvient du cerisier, et de la dînette.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -10329,7 +10850,21 @@
       <c r="AV54" s="2" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>narrateur|Adam rejoint une pomme. la dînette est rangé. Léa est fini. Le sol est un peu froid. Maman n'est pas loin. Adam les rejoint. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Adam dit merci à papa.</t>
+          <t>narrateur|Une pomme rentre dans une petite assiette.
+narrateur|Le cerisier laisse tomber un pétale.
+narrateur|Aniss a choisi le cerisier.
+narrateur|Puis la dînette. Puis une pomme.
+narrateur|Mila a encore de l'énergie.
+papa|Cette énergie n'est pas une faute.
+maman|On peut jouer ou attendre.
+enfant-m|On joue ou on attend.
+papa|On peut demander à un adulte.
+enfant-m|Merci, papa.
+maman|Bravo, Aniss.
+maman|C'est du bon travail.
+enfant-f|Merci, maman.
+narrateur|Le jardin redevient calme, tout doux.
+narrateur|Aniss se souvient du cerisier, et de la dînette.</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr"/>
@@ -10357,7 +10892,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Mila a de l'énergie. Ce n'est pas une faute. On a joué ou on a attendu. Bravo, Aniss. Tu as fait du bon travail. Aniss a visité le cerisier. Il a pris la dînette. Il a goûté une pomme. La petite assiette a un pétale, tout drôle. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -10497,7 +11032,16 @@
       <c r="AV55" s="2" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Mila a de l'énergie.
+enfant-m|Ce n'est pas une faute.
+papa|On a joué ou on a attendu.
+maman|Bravo, Aniss.
+papa|Tu as fait du bon travail.
+narrateur|Aniss a visité le cerisier.
+narrateur|Il a pris la dînette.
+narrateur|Il a goûté une pomme.
+narrateur|La petite assiette a un pétale, tout drôle.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr"/>
@@ -10525,7 +11069,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Près de un yaourt. Adam pose la dînette. Léa est derrière. Ça sent le pain chaud. Adam range la tasse. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Adam dit merci à papa.</t>
+          <t>Un yaourt fait un goûter de poupée. La dînette est sous les branches. Aniss a choisi le cerisier. Puis la dînette. Puis un yaourt. Mila a encore de l'énergie. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue ou on attend. On peut demander à un adulte. Merci, papa. Bravo, Aniss. C'est du bon travail. Merci, maman. Le jardin redevient calme, tout doux. Aniss se souvient du cerisier, et de la dînette.</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -10665,7 +11209,21 @@
       <c r="AV56" s="2" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>narrateur|Près de un yaourt. Adam pose la dînette. Léa est derrière. Ça sent le pain chaud. Adam range la tasse. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Adam dit merci à papa.</t>
+          <t>narrateur|Un yaourt fait un goûter de poupée.
+narrateur|La dînette est sous les branches.
+narrateur|Aniss a choisi le cerisier.
+narrateur|Puis la dînette. Puis un yaourt.
+narrateur|Mila a encore de l'énergie.
+papa|Cette énergie n'est pas une faute.
+maman|On peut jouer ou attendre.
+enfant-m|On joue ou on attend.
+papa|On peut demander à un adulte.
+enfant-m|Merci, papa.
+maman|Bravo, Aniss.
+maman|C'est du bon travail.
+enfant-f|Merci, maman.
+narrateur|Le jardin redevient calme, tout doux.
+narrateur|Aniss se souvient du cerisier, et de la dînette.</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr"/>
@@ -10693,7 +11251,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Mila a de l'énergie. Ce n'est pas une faute. On a joué ou on a attendu. Bravo, Aniss. Tu as fait du bon travail. Aniss a visité le cerisier. Il a pris la dînette. Il a goûté un yaourt. Une fourmi a visité la soucoupe, puis elle est partie. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -10833,7 +11391,16 @@
       <c r="AV57" s="2" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Mila a de l'énergie.
+enfant-m|Ce n'est pas une faute.
+papa|On a joué ou on a attendu.
+maman|Bravo, Aniss.
+papa|Tu as fait du bon travail.
+narrateur|Aniss a visité le cerisier.
+narrateur|Il a pris la dînette.
+narrateur|Il a goûté un yaourt.
+narrateur|Une fourmi a visité la soucoupe, puis elle est partie.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr"/>
@@ -10861,7 +11428,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Adam montre un morceau de pain. Papa a vu Léa. Et la dînette. On dit merci. Adam essuie ses mains. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Adam dit merci à papa.</t>
+          <t>Un morceau de pain sert de tartine. Une abeille passe près de la tasse. Aniss a choisi le cerisier. Puis la dînette. Puis un morceau de pain. Mila a encore de l'énergie. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue ou on attend. On peut demander à un adulte. Merci, papa. Bravo, Aniss. C'est du bon travail. Merci, maman. Le jardin redevient calme, tout doux. Aniss se souvient du cerisier, et de la dînette.</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -11001,7 +11568,21 @@
       <c r="AV58" s="2" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>narrateur|Adam montre un morceau de pain. Papa a vu Léa. Et la dînette. On dit merci. Adam essuie ses mains. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Adam dit merci à papa.</t>
+          <t>narrateur|Un morceau de pain sert de tartine.
+narrateur|Une abeille passe près de la tasse.
+narrateur|Aniss a choisi le cerisier.
+narrateur|Puis la dînette. Puis un morceau de pain.
+narrateur|Mila a encore de l'énergie.
+papa|Cette énergie n'est pas une faute.
+maman|On peut jouer ou attendre.
+enfant-m|On joue ou on attend.
+papa|On peut demander à un adulte.
+enfant-m|Merci, papa.
+maman|Bravo, Aniss.
+maman|C'est du bon travail.
+enfant-f|Merci, maman.
+narrateur|Le jardin redevient calme, tout doux.
+narrateur|Aniss se souvient du cerisier, et de la dînette.</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr"/>
@@ -11029,7 +11610,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Mila a de l'énergie. Ce n'est pas une faute. On a joué ou on a attendu. Bravo, Aniss. Tu as fait du bon travail. Aniss a visité le cerisier. Il a pris la dînette. Il a goûté un morceau de pain. Le linge rose a claqué, tout loin. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -11169,7 +11750,16 @@
       <c r="AV59" s="2" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Mila a de l'énergie.
+enfant-m|Ce n'est pas une faute.
+papa|On a joué ou on a attendu.
+maman|Bravo, Aniss.
+papa|Tu as fait du bon travail.
+narrateur|Aniss a visité le cerisier.
+narrateur|Il a pris la dînette.
+narrateur|Il a goûté un morceau de pain.
+narrateur|Le linge rose a claqué, tout loin.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr"/>
@@ -11197,7 +11787,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Adam rejoint Sami. Sami tourne, puis s'assoit. Il a beaucoup d'énergie. Cette énergie n'est pas une faute. Adam joue un moment, puis attend. Papa reste tout près. On peut jouer ensemble.</t>
+          <t>Aniss va vers le banc. Le bois est tiède, un peu lisse. Un escargot avance, tout lent. Mila tourne. Puis elle s'assoit. Elle a beaucoup d'énergie. Cette énergie n'est pas une faute. On peut jouer ou attendre. Elle s'assoit. Puis elle se lève. On attend. Puis on joue. Mila pose une main sur le bois. Tu peux demander à papa. On joue, ou on attend ? Les deux. Ce n'est pas une faute. Bravo. Tu as demandé. Le banc garde une trace de soleil.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -11337,7 +11927,21 @@
       <c r="AV60" s="2" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>narrateur|Adam rejoint Sami. Sami tourne, puis s'assoit. Il a beaucoup d'énergie. Cette énergie n'est pas une faute. Adam joue un moment, puis attend. Papa reste tout près. On peut jouer ensemble.</t>
+          <t>narrateur|Aniss va vers le banc.
+narrateur|Le bois est tiède, un peu lisse.
+narrateur|Un escargot avance, tout lent.
+narrateur|Mila tourne. Puis elle s'assoit.
+narrateur|Elle a beaucoup d'énergie.
+papa|Cette énergie n'est pas une faute.
+maman|On peut jouer ou attendre.
+enfant-m|Elle s'assoit. Puis elle se lève.
+papa|On attend. Puis on joue.
+narrateur|Mila pose une main sur le bois.
+maman|Tu peux demander à papa.
+enfant-m|On joue, ou on attend ?
+maman|Les deux. Ce n'est pas une faute.
+papa|Bravo. Tu as demandé.
+narrateur|Le banc garde une trace de soleil.</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr"/>
@@ -11549,7 +12153,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Oui. Cette énergie n'est pas une faute. On peut jouer ou attendre. Adam hoche la tête. On continue, avec papa. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut jouer ensemble.</t>
+          <t>Oui. On demande à un adulte. Cette énergie n'est pas une faute. Aniss hoche la tête. On peut jouer ou attendre. Bravo, Aniss. Merci, maman. C'est du bon travail.</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -11693,7 +12297,14 @@
       </c>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>narrateur|Oui. Cette énergie n'est pas une faute. On peut jouer ou attendre. Adam hoche la tête. On continue, avec papa. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut jouer ensemble.</t>
+          <t>narrateur|Oui.
+papa|On demande à un adulte.
+maman|Cette énergie n'est pas une faute.
+narrateur|Aniss hoche la tête.
+papa|On peut jouer ou attendre.
+maman|Bravo, Aniss.
+enfant-m|Merci, maman.
+papa|C'est du bon travail.</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr"/>
@@ -11721,7 +12332,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre les cubes, le livre, ou la dînette.</t>
+          <t>On prend quel jeu ? Les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -11885,7 +12496,8 @@
       <c r="AV63" s="2" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+          <t>narrateur|On prend quel jeu ?
+maman|Les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr"/>
@@ -11913,7 +12525,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Sami veut les cubes. Il court les chercher. Cette énergie n'est pas une faute. Adam peut jouer ou attendre. Papa reste tout près. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut jouer ensemble.</t>
+          <t>Près de le banc, Mila veut les cubes. Les cubes sont en bois, un peu rudes. Un cube rouge fait toc, sur l'herbe. Mila bouge beaucoup, encore. Cette énergie n'est pas une faute. On peut jouer ou attendre. J'attends mon tour. Oui. Puis on joue ensemble. Mila pose un cube. Puis elle reprend. Tu peux demander à papa. Papa, c'est mon tour ? Oui. Bravo, Aniss. Le cube rouge reste dans sa main.</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -12053,7 +12665,19 @@
       <c r="AV64" s="2" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>narrateur|Sami veut les cubes. Il court les chercher. Cette énergie n'est pas une faute. Adam peut jouer ou attendre. Papa reste tout près. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut jouer ensemble.</t>
+          <t>narrateur|Près de le banc, Mila veut les cubes.
+narrateur|Les cubes sont en bois, un peu rudes.
+narrateur|Un cube rouge fait toc, sur l'herbe.
+narrateur|Mila bouge beaucoup, encore.
+papa|Cette énergie n'est pas une faute.
+maman|On peut jouer ou attendre.
+enfant-m|J'attends mon tour.
+papa|Oui. Puis on joue ensemble.
+narrateur|Mila pose un cube. Puis elle reprend.
+maman|Tu peux demander à papa.
+enfant-m|Papa, c'est mon tour ?
+papa|Oui. Bravo, Aniss.
+narrateur|Le cube rouge reste dans sa main.</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr"/>
@@ -12081,7 +12705,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+          <t>On prend quel goûter ? Une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -12245,7 +12869,8 @@
       <c r="AV65" s="2" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+          <t>narrateur|On prend quel goûter ?
+papa|Une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr"/>
@@ -12273,7 +12898,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Adam a choisi Sami. Puis les cubes. Puis une pomme. Un crochet tient bien le manteau. J'ai appris. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Adam dit merci à papa.</t>
+          <t>Une pomme roule sous le banc. Un cube rouge tape le bois, tout doux. Aniss a choisi le banc. Puis les cubes. Puis une pomme. Mila a encore de l'énergie. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue ou on attend. On peut demander à un adulte. Merci, papa. Bravo, Aniss. C'est du bon travail. Merci, maman. Le jardin redevient calme, tout doux. Aniss se souvient du banc, et des cubes.</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -12413,9 +13038,21 @@
       <c r="AV66" s="2" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>narrateur|Adam a choisi Sami. Puis les cubes. Puis une pomme. Un crochet tient bien le manteau.
-enfant-m|J'ai appris. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte.
-narrateur|Adam dit merci à papa.</t>
+          <t>narrateur|Une pomme roule sous le banc.
+narrateur|Un cube rouge tape le bois, tout doux.
+narrateur|Aniss a choisi le banc.
+narrateur|Puis les cubes. Puis une pomme.
+narrateur|Mila a encore de l'énergie.
+papa|Cette énergie n'est pas une faute.
+maman|On peut jouer ou attendre.
+enfant-m|On joue ou on attend.
+papa|On peut demander à un adulte.
+enfant-m|Merci, papa.
+maman|Bravo, Aniss.
+maman|C'est du bon travail.
+enfant-f|Merci, maman.
+narrateur|Le jardin redevient calme, tout doux.
+narrateur|Aniss se souvient du banc, et des cubes.</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr"/>
@@ -12443,7 +13080,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Mila a de l'énergie. Ce n'est pas une faute. On a joué ou on a attendu. Bravo, Aniss. Tu as fait du bon travail. Aniss a visité le banc. Il a pris les cubes. Il a goûté une pomme. Le bois du banc est encore tiède. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -12583,7 +13220,16 @@
       <c r="AV67" s="2" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Mila a de l'énergie.
+enfant-m|Ce n'est pas une faute.
+papa|On a joué ou on a attendu.
+maman|Bravo, Aniss.
+papa|Tu as fait du bon travail.
+narrateur|Aniss a visité le banc.
+narrateur|Il a pris les cubes.
+narrateur|Il a goûté une pomme.
+narrateur|Le bois du banc est encore tiède.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr"/>
@@ -12611,7 +13257,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Adam s'arrête près de un yaourt. les cubes est rangé. L'eau coule, tout petit bruit. Adam ferme la porte, tout doux. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Adam dit merci à papa.</t>
+          <t>Un yaourt reste au frais, sur le banc. Les cubes font un petit tas. Aniss a choisi le banc. Puis les cubes. Puis un yaourt. Mila a encore de l'énergie. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue ou on attend. On peut demander à un adulte. Merci, papa. Bravo, Aniss. C'est du bon travail. Merci, maman. Le jardin redevient calme, tout doux. Aniss se souvient du banc, et des cubes.</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -12751,7 +13397,21 @@
       <c r="AV68" s="2" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>narrateur|Adam s'arrête près de un yaourt. les cubes est rangé. L'eau coule, tout petit bruit. Adam ferme la porte, tout doux. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Adam dit merci à papa.</t>
+          <t>narrateur|Un yaourt reste au frais, sur le banc.
+narrateur|Les cubes font un petit tas.
+narrateur|Aniss a choisi le banc.
+narrateur|Puis les cubes. Puis un yaourt.
+narrateur|Mila a encore de l'énergie.
+papa|Cette énergie n'est pas une faute.
+maman|On peut jouer ou attendre.
+enfant-m|On joue ou on attend.
+papa|On peut demander à un adulte.
+enfant-m|Merci, papa.
+maman|Bravo, Aniss.
+maman|C'est du bon travail.
+enfant-f|Merci, maman.
+narrateur|Le jardin redevient calme, tout doux.
+narrateur|Aniss se souvient du banc, et des cubes.</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr"/>
@@ -12779,7 +13439,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Mila a de l'énergie. Ce n'est pas une faute. On a joué ou on a attendu. Bravo, Aniss. Tu as fait du bon travail. Aniss a visité le banc. Il a pris les cubes. Il a goûté un yaourt. Un escargot a avancé près du pied. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -12919,7 +13579,16 @@
       <c r="AV69" s="2" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Mila a de l'énergie.
+enfant-m|Ce n'est pas une faute.
+papa|On a joué ou on a attendu.
+maman|Bravo, Aniss.
+papa|Tu as fait du bon travail.
+narrateur|Aniss a visité le banc.
+narrateur|Il a pris les cubes.
+narrateur|Il a goûté un yaourt.
+narrateur|Un escargot a avancé près du pied.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr"/>
@@ -12947,7 +13616,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Adam se souvient de Sami. Et de les cubes. Et de un morceau de pain. La lumière est claire. Adam marche près de papa. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Adam dit merci à papa.</t>
+          <t>Un morceau de pain attend sur le bois. Un cube jaune a une miette. Aniss a choisi le banc. Puis les cubes. Puis un morceau de pain. Mila a encore de l'énergie. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue ou on attend. On peut demander à un adulte. Merci, papa. Bravo, Aniss. C'est du bon travail. Merci, maman. Le jardin redevient calme, tout doux. Aniss se souvient du banc, et des cubes.</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -13087,7 +13756,21 @@
       <c r="AV70" s="2" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>narrateur|Adam se souvient de Sami. Et de les cubes. Et de un morceau de pain. La lumière est claire. Adam marche près de papa. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Adam dit merci à papa.</t>
+          <t>narrateur|Un morceau de pain attend sur le bois.
+narrateur|Un cube jaune a une miette.
+narrateur|Aniss a choisi le banc.
+narrateur|Puis les cubes. Puis un morceau de pain.
+narrateur|Mila a encore de l'énergie.
+papa|Cette énergie n'est pas une faute.
+maman|On peut jouer ou attendre.
+enfant-m|On joue ou on attend.
+papa|On peut demander à un adulte.
+enfant-m|Merci, papa.
+maman|Bravo, Aniss.
+maman|C'est du bon travail.
+enfant-f|Merci, maman.
+narrateur|Le jardin redevient calme, tout doux.
+narrateur|Aniss se souvient du banc, et des cubes.</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr"/>
@@ -13115,7 +13798,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Mila a de l'énergie. Ce n'est pas une faute. On a joué ou on a attendu. Bravo, Aniss. Tu as fait du bon travail. Aniss a visité le banc. Il a pris les cubes. Il a goûté un morceau de pain. Le seau jaune a gardé une miette. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -13255,7 +13938,16 @@
       <c r="AV71" s="2" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Mila a de l'énergie.
+enfant-m|Ce n'est pas une faute.
+papa|On a joué ou on a attendu.
+maman|Bravo, Aniss.
+papa|Tu as fait du bon travail.
+narrateur|Aniss a visité le banc.
+narrateur|Il a pris les cubes.
+narrateur|Il a goûté un morceau de pain.
+narrateur|Le seau jaune a gardé une miette.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr"/>
@@ -13283,7 +13975,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Sami veut le livre. Il s'assoit, puis se lève. Cette énergie n'est pas une faute. Adam peut jouer ou attendre. Papa montre le geste, lentement. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut jouer ensemble.</t>
+          <t>Près de le banc, Mila veut le livre. La couverture est un peu rêche. Une page chuchote sous le doigt. Mila tourne les pages, tout vite. Cette énergie n'est pas une faute. On peut jouer ou attendre. On attend un peu. Oui. Puis on lit ensemble. Mila souffle. Elle pose le livre. Tu peux demander à maman. Maman, on lit ? Oui. Bravo. Tu as attendu. Un pétale reste sur la page.</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -13423,7 +14115,19 @@
       <c r="AV72" s="2" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>narrateur|Sami veut le livre. Il s'assoit, puis se lève. Cette énergie n'est pas une faute. Adam peut jouer ou attendre. Papa montre le geste, lentement. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut jouer ensemble.</t>
+          <t>narrateur|Près de le banc, Mila veut le livre.
+narrateur|La couverture est un peu rêche.
+narrateur|Une page chuchote sous le doigt.
+narrateur|Mila tourne les pages, tout vite.
+maman|Cette énergie n'est pas une faute.
+papa|On peut jouer ou attendre.
+enfant-m|On attend un peu.
+maman|Oui. Puis on lit ensemble.
+narrateur|Mila souffle. Elle pose le livre.
+papa|Tu peux demander à maman.
+enfant-m|Maman, on lit ?
+maman|Oui. Bravo. Tu as attendu.
+narrateur|Un pétale reste sur la page.</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr"/>
@@ -13451,7 +14155,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+          <t>On prend quel goûter ? Une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -13615,7 +14319,8 @@
       <c r="AV73" s="2" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+          <t>narrateur|On prend quel goûter ?
+papa|Une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr"/>
@@ -13643,7 +14348,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Avec une pomme. Après le livre. Près de Sami. Adam s'arrête. Un vélo passe au loin. Adam écoute papa encore une fois. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Adam dit merci à papa.</t>
+          <t>Une pomme brille près du livre. Le banc est tiède, encore. Aniss a choisi le banc. Puis le livre. Puis une pomme. Mila a encore de l'énergie. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue ou on attend. On peut demander à un adulte. Merci, papa. Bravo, Aniss. C'est du bon travail. Merci, maman. Le jardin redevient calme, tout doux. Aniss se souvient du banc, et du livre.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -13783,7 +14488,21 @@
       <c r="AV74" s="2" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>narrateur|Avec une pomme. Après le livre. Près de Sami. Adam s'arrête. Un vélo passe au loin. Adam écoute papa encore une fois. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Adam dit merci à papa.</t>
+          <t>narrateur|Une pomme brille près du livre.
+narrateur|Le banc est tiède, encore.
+narrateur|Aniss a choisi le banc.
+narrateur|Puis le livre. Puis une pomme.
+narrateur|Mila a encore de l'énergie.
+papa|Cette énergie n'est pas une faute.
+maman|On peut jouer ou attendre.
+enfant-m|On joue ou on attend.
+papa|On peut demander à un adulte.
+enfant-m|Merci, papa.
+maman|Bravo, Aniss.
+maman|C'est du bon travail.
+enfant-f|Merci, maman.
+narrateur|Le jardin redevient calme, tout doux.
+narrateur|Aniss se souvient du banc, et du livre.</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr"/>
@@ -13811,7 +14530,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Mila a de l'énergie. Ce n'est pas une faute. On a joué ou on a attendu. Bravo, Aniss. Tu as fait du bon travail. Aniss a visité le banc. Il a pris le livre. Il a goûté une pomme. Le tuyau a fait chhh, tout doux. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -13951,7 +14670,16 @@
       <c r="AV75" s="2" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Mila a de l'énergie.
+enfant-m|Ce n'est pas une faute.
+papa|On a joué ou on a attendu.
+maman|Bravo, Aniss.
+papa|Tu as fait du bon travail.
+narrateur|Aniss a visité le banc.
+narrateur|Il a pris le livre.
+narrateur|Il a goûté une pomme.
+narrateur|Le tuyau a fait chhh, tout doux.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr"/>
@@ -13979,7 +14707,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Adam range le livre. un yaourt reste près de Sami. Une chaussette est encore sablée. Adam ferme le sac. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Adam dit merci à papa.</t>
+          <t>Un yaourt cliquette sur le banc. Le livre a une ombre de linge. Aniss a choisi le banc. Puis le livre. Puis un yaourt. Mila a encore de l'énergie. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue ou on attend. On peut demander à un adulte. Merci, papa. Bravo, Aniss. C'est du bon travail. Merci, maman. Le jardin redevient calme, tout doux. Aniss se souvient du banc, et du livre.</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -14119,7 +14847,21 @@
       <c r="AV76" s="2" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>narrateur|Adam range le livre. un yaourt reste près de Sami. Une chaussette est encore sablée. Adam ferme le sac. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Adam dit merci à papa.</t>
+          <t>narrateur|Un yaourt cliquette sur le banc.
+narrateur|Le livre a une ombre de linge.
+narrateur|Aniss a choisi le banc.
+narrateur|Puis le livre. Puis un yaourt.
+narrateur|Mila a encore de l'énergie.
+papa|Cette énergie n'est pas une faute.
+maman|On peut jouer ou attendre.
+enfant-m|On joue ou on attend.
+papa|On peut demander à un adulte.
+enfant-m|Merci, papa.
+maman|Bravo, Aniss.
+maman|C'est du bon travail.
+enfant-f|Merci, maman.
+narrateur|Le jardin redevient calme, tout doux.
+narrateur|Aniss se souvient du banc, et du livre.</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr"/>
@@ -14147,7 +14889,7 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Mila a de l'énergie. Ce n'est pas une faute. On a joué ou on a attendu. Bravo, Aniss. Tu as fait du bon travail. Aniss a visité le banc. Il a pris le livre. Il a goûté un yaourt. Un papillon a touché la page, puis parti. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -14287,7 +15029,16 @@
       <c r="AV77" s="2" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Mila a de l'énergie.
+enfant-m|Ce n'est pas une faute.
+papa|On a joué ou on a attendu.
+maman|Bravo, Aniss.
+papa|Tu as fait du bon travail.
+narrateur|Aniss a visité le banc.
+narrateur|Il a pris le livre.
+narrateur|Il a goûté un yaourt.
+narrateur|Un papillon a touché la page, puis parti.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr"/>
@@ -14315,7 +15066,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Un morceau de pain est là. le livre aussi. Sami reste dans le souvenir. Une tasse cliquette. Adam raccroche un linge. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Adam dit merci à papa.</t>
+          <t>Un morceau de pain sent le bois chaud. Une page du livre claque, tout léger. Aniss a choisi le banc. Puis le livre. Puis un morceau de pain. Mila a encore de l'énergie. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue ou on attend. On peut demander à un adulte. Merci, papa. Bravo, Aniss. C'est du bon travail. Merci, maman. Le jardin redevient calme, tout doux. Aniss se souvient du banc, et du livre.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -14455,7 +15206,21 @@
       <c r="AV78" s="2" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>narrateur|Un morceau de pain est là. le livre aussi. Sami reste dans le souvenir. Une tasse cliquette. Adam raccroche un linge. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Adam dit merci à papa.</t>
+          <t>narrateur|Un morceau de pain sent le bois chaud.
+narrateur|Une page du livre claque, tout léger.
+narrateur|Aniss a choisi le banc.
+narrateur|Puis le livre. Puis un morceau de pain.
+narrateur|Mila a encore de l'énergie.
+papa|Cette énergie n'est pas une faute.
+maman|On peut jouer ou attendre.
+enfant-m|On joue ou on attend.
+papa|On peut demander à un adulte.
+enfant-m|Merci, papa.
+maman|Bravo, Aniss.
+maman|C'est du bon travail.
+enfant-f|Merci, maman.
+narrateur|Le jardin redevient calme, tout doux.
+narrateur|Aniss se souvient du banc, et du livre.</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr"/>
@@ -14483,7 +15248,7 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Mila a de l'énergie. Ce n'est pas une faute. On a joué ou on a attendu. Bravo, Aniss. Tu as fait du bon travail. Aniss a visité le banc. Il a pris le livre. Il a goûté un morceau de pain. L'herbe mouillée brille encore, sous le banc. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -14623,7 +15388,16 @@
       <c r="AV79" s="2" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Mila a de l'énergie.
+enfant-m|Ce n'est pas une faute.
+papa|On a joué ou on a attendu.
+maman|Bravo, Aniss.
+papa|Tu as fait du bon travail.
+narrateur|Aniss a visité le banc.
+narrateur|Il a pris le livre.
+narrateur|Il a goûté un morceau de pain.
+narrateur|L'herbe mouillée brille encore, sous le banc.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr"/>
@@ -14651,7 +15425,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Sami veut la dînette. Il sert très vite. Cette énergie n'est pas une faute. Adam peut jouer ou attendre. Je suis là. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut jouer ensemble.</t>
+          <t>Près de le banc, Mila veut la dînette. Une petite tasse sonne, tout creux. Ça sent presque la soupe, pour de rire. Mila range. Puis elle dérange. Cette énergie n'est pas une faute. On peut jouer ou attendre. On sert à tour de rôle. Oui. On attend son tour. Mila pose la cuillère, tout doux. Tu as demandé. C'est bien. Merci, maman. Bravo, vous deux. La petite casserole reste au calme.</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -14791,8 +15565,19 @@
       <c r="AV80" s="2" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>narrateur|Sami veut la dînette. Il sert très vite. Cette énergie n'est pas une faute. Adam peut jouer ou attendre.
-papa|Je suis là. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut jouer ensemble.</t>
+          <t>narrateur|Près de le banc, Mila veut la dînette.
+narrateur|Une petite tasse sonne, tout creux.
+narrateur|Ça sent presque la soupe, pour de rire.
+narrateur|Mila range. Puis elle dérange.
+papa|Cette énergie n'est pas une faute.
+maman|On peut jouer ou attendre.
+enfant-m|On sert à tour de rôle.
+papa|Oui. On attend son tour.
+narrateur|Mila pose la cuillère, tout doux.
+maman|Tu as demandé. C'est bien.
+enfant-m|Merci, maman.
+papa|Bravo, vous deux.
+narrateur|La petite casserole reste au calme.</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr"/>
@@ -14820,7 +15605,7 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+          <t>On prend quel goûter ? Une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
@@ -14984,7 +15769,8 @@
       <c r="AV81" s="2" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+          <t>narrateur|On prend quel goûter ?
+papa|Une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr"/>
@@ -15012,7 +15798,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Adam rejoint une pomme. la dînette est rangé. Sami est fini. Un panier est posé sur le banc. Adam boit une gorgée d'eau. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Adam dit merci à papa.</t>
+          <t>Une pomme devient un gâteau de banc. La dînette sonne contre le bois. Aniss a choisi le banc. Puis la dînette. Puis une pomme. Mila a encore de l'énergie. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue ou on attend. On peut demander à un adulte. Merci, papa. Bravo, Aniss. C'est du bon travail. Merci, maman. Le jardin redevient calme, tout doux. Aniss se souvient du banc, et de la dînette.</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -15152,7 +15938,21 @@
       <c r="AV82" s="2" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>narrateur|Adam rejoint une pomme. la dînette est rangé. Sami est fini. Un panier est posé sur le banc. Adam boit une gorgée d'eau. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Adam dit merci à papa.</t>
+          <t>narrateur|Une pomme devient un gâteau de banc.
+narrateur|La dînette sonne contre le bois.
+narrateur|Aniss a choisi le banc.
+narrateur|Puis la dînette. Puis une pomme.
+narrateur|Mila a encore de l'énergie.
+papa|Cette énergie n'est pas une faute.
+maman|On peut jouer ou attendre.
+enfant-m|On joue ou on attend.
+papa|On peut demander à un adulte.
+enfant-m|Merci, papa.
+maman|Bravo, Aniss.
+maman|C'est du bon travail.
+enfant-f|Merci, maman.
+narrateur|Le jardin redevient calme, tout doux.
+narrateur|Aniss se souvient du banc, et de la dînette.</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr"/>
@@ -15180,7 +15980,7 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Mila a de l'énergie. Ce n'est pas une faute. On a joué ou on a attendu. Bravo, Aniss. Tu as fait du bon travail. Aniss a visité le banc. Il a pris la dînette. Il a goûté une pomme. La balançoire vide a bougé, tout léger. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -15320,7 +16120,16 @@
       <c r="AV83" s="2" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Mila a de l'énergie.
+enfant-m|Ce n'est pas une faute.
+papa|On a joué ou on a attendu.
+maman|Bravo, Aniss.
+papa|Tu as fait du bon travail.
+narrateur|Aniss a visité le banc.
+narrateur|Il a pris la dînette.
+narrateur|Il a goûté une pomme.
+narrateur|La balançoire vide a bougé, tout léger.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr"/>
@@ -15348,7 +16157,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Près de un yaourt. Adam pose la dînette. Sami est derrière. On attend son tour. Adam prend la main de papa. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Adam dit merci à papa.</t>
+          <t>Un yaourt refroidit la petite cuillère. Le banc garde la dînette, tout calme. Aniss a choisi le banc. Puis la dînette. Puis un yaourt. Mila a encore de l'énergie. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue ou on attend. On peut demander à un adulte. Merci, papa. Bravo, Aniss. C'est du bon travail. Merci, maman. Le jardin redevient calme, tout doux. Aniss se souvient du banc, et de la dînette.</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -15488,7 +16297,21 @@
       <c r="AV84" s="2" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>narrateur|Près de un yaourt. Adam pose la dînette. Sami est derrière. On attend son tour. Adam prend la main de papa. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Adam dit merci à papa.</t>
+          <t>narrateur|Un yaourt refroidit la petite cuillère.
+narrateur|Le banc garde la dînette, tout calme.
+narrateur|Aniss a choisi le banc.
+narrateur|Puis la dînette. Puis un yaourt.
+narrateur|Mila a encore de l'énergie.
+papa|Cette énergie n'est pas une faute.
+maman|On peut jouer ou attendre.
+enfant-m|On joue ou on attend.
+papa|On peut demander à un adulte.
+enfant-m|Merci, papa.
+maman|Bravo, Aniss.
+maman|C'est du bon travail.
+enfant-f|Merci, maman.
+narrateur|Le jardin redevient calme, tout doux.
+narrateur|Aniss se souvient du banc, et de la dînette.</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr"/>
@@ -15516,7 +16339,7 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Mila a de l'énergie. Ce n'est pas une faute. On a joué ou on a attendu. Bravo, Aniss. Tu as fait du bon travail. Aniss a visité le banc. Il a pris la dînette. Il a goûté un yaourt. Une feuille de menthe sent encore, tout près. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -15656,7 +16479,16 @@
       <c r="AV85" s="2" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Mila a de l'énergie.
+enfant-m|Ce n'est pas une faute.
+papa|On a joué ou on a attendu.
+maman|Bravo, Aniss.
+papa|Tu as fait du bon travail.
+narrateur|Aniss a visité le banc.
+narrateur|Il a pris la dînette.
+narrateur|Il a goûté un yaourt.
+narrateur|Une feuille de menthe sent encore, tout près.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr"/>
@@ -15684,7 +16516,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Adam montre un morceau de pain. Papa a vu Sami. Et la dînette. Un galet est encore chaud. Adam range encore un peu, près de papa. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Adam dit merci à papa.</t>
+          <t>Un morceau de pain a des miettes. La dînette rentre dans la boîte. Aniss a choisi le banc. Puis la dînette. Puis un morceau de pain. Mila a encore de l'énergie. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue ou on attend. On peut demander à un adulte. Merci, papa. Bravo, Aniss. C'est du bon travail. Merci, maman. Le jardin redevient calme, tout doux. Aniss se souvient du banc, et de la dînette.</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -15824,7 +16656,21 @@
       <c r="AV86" s="2" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>narrateur|Adam montre un morceau de pain. Papa a vu Sami. Et la dînette. Un galet est encore chaud. Adam range encore un peu, près de papa. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Adam dit merci à papa.</t>
+          <t>narrateur|Un morceau de pain a des miettes.
+narrateur|La dînette rentre dans la boîte.
+narrateur|Aniss a choisi le banc.
+narrateur|Puis la dînette. Puis un morceau de pain.
+narrateur|Mila a encore de l'énergie.
+papa|Cette énergie n'est pas une faute.
+maman|On peut jouer ou attendre.
+enfant-m|On joue ou on attend.
+papa|On peut demander à un adulte.
+enfant-m|Merci, papa.
+maman|Bravo, Aniss.
+maman|C'est du bon travail.
+enfant-f|Merci, maman.
+narrateur|Le jardin redevient calme, tout doux.
+narrateur|Aniss se souvient du banc, et de la dînette.</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr"/>
@@ -15852,7 +16698,7 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Mila a de l'énergie. Ce n'est pas une faute. On a joué ou on a attendu. Bravo, Aniss. Tu as fait du bon travail. Aniss a visité le banc. Il a pris la dînette. Il a goûté un morceau de pain. Une trace de botte reste sur la dalle. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
@@ -15992,7 +16838,16 @@
       <c r="AV87" s="2" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Mila a de l'énergie.
+enfant-m|Ce n'est pas une faute.
+papa|On a joué ou on a attendu.
+maman|Bravo, Aniss.
+papa|Tu as fait du bon travail.
+narrateur|Aniss a visité le banc.
+narrateur|Il a pris la dînette.
+narrateur|Il a goûté un morceau de pain.
+narrateur|Une trace de botte reste sur la dalle.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr"/>
@@ -16014,7 +16869,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16052,6 +16907,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-DIF-006.xlsx
+++ b/stories/arbres/TREE-DIF-006.xlsx
@@ -1197,12 +1197,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Une goutte quitte l'arrosoir. Elle fait ploc sur la dalle chaude. Derrière la maison, le jardin est minuscule. Ça sent la terre, et un peu la menthe. Un linge rose sèche près du cerisier. Les bottes de papa cuisent au soleil. Maman a laissé l'arrosoir dans les fleurs. En ce moment, Raphaël s'accroupit. Une petite tête penche, trop sèche. Elle a soif ! Je n'ai pas vu celle-là. Il reste des gouttes, tu crois ? Je les porte ! Il saisit l'arrosoir à deux mains. L'eau chante, puis elle danse. Doucement, elle n'aime pas les vagues. Je vais trop vite. Tu peux choisir une fleur. Une jaune attend près du bac. Une rouge attend près des tomates. Une bleue attend près du banc. Merci d'avoir vu sa soif. Quelle couleur, Raphaël ?</t>
+          <t>Une goutte quitte l'arrosoir. Elle fait ploc sur la dalle chaude. Derrière la maison, le jardin est minuscule. Ça sent la terre, et un peu la menthe. Un linge rose sèche près du cerisier. Les bottes de papa cuisent au soleil. Maman a laissé l'arrosoir dans les fleurs. En ce moment, Raphaël s'accroupit. Une petite tête penche, trop sèche. Elle a soif ! Je n'ai pas vu celle-là. Il reste des gouttes, tu crois ? Je les porte ! Il saisit l'arrosoir à deux mains. L'eau chante, puis elle danse. Doucement, elle n'aime pas les vagues. Je vais trop vite. Tu peux choisir une fleur. Une jaune attend près du bac. Plus loin, une rouge se tient près des tomates. À l'ombre, une bleue penche près du banc. Merci d'avoir vu sa soif. Quelle couleur, Raphaël ?</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Une goutte quitte l'arrosoir. Elle fait ploc sur la dalle chaude. Derrière la maison, le jardin est minuscule. Ça sent la terre, et un peu la menthe. Un linge rose sèche près du cerisier. Les bottes de papa cuisent au soleil. Maman a laissé l'arrosoir dans les fleurs. En ce moment, Raphaël s'accroupit. Une petite tête penche, trop sèche. Elle a soif ! Je n'ai pas vu celle-là. Il reste des gouttes, tu crois ? Je les porte ! Il saisit l'arrosoir à deux mains. L'eau chante, puis elle danse. Doucement, elle n'aime pas les vagues. Je vais trop vite. Tu peux choisir une fleur. Une jaune attend près du bac. Une rouge attend près des tomates. Une bleue attend près du banc. Merci d'avoir vu sa soif. Quelle couleur, Raphaël ?</t>
+          <t>Une goutte quitte l'arrosoir. Elle fait ploc sur la dalle chaude. Derrière la maison, le jardin est minuscule. Ça sent la terre, et un peu la menthe. Un linge rose sèche près du cerisier. Les bottes de papa cuisent au soleil. Maman a laissé l'arrosoir dans les fleurs. En ce moment, Raphaël s'accroupit. Une petite tête penche, trop sèche. Elle a soif ! Je n'ai pas vu celle-là. Il reste des gouttes, tu crois ? Je les porte ! Il saisit l'arrosoir à deux mains. L'eau chante, puis elle danse. Doucement, elle n'aime pas les vagues. Je vais trop vite. Tu peux choisir une fleur. Une jaune attend près du bac. Plus loin, une rouge se tient près des tomates. À l'ombre, une bleue penche près du banc. Merci d'avoir vu sa soif. Quelle couleur, Raphaël ?</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1356,8 +1356,8 @@
 enfant-m|Je vais trop vite.
 maman|Tu peux choisir une fleur.
 narrateur|Une jaune attend près du bac.
-narrateur|Une rouge attend près des tomates.
-narrateur|Une bleue attend près du banc.
+narrateur|Plus loin, une rouge se tient près des tomates.
+narrateur|À l'ombre, une bleue penche près du banc.
 papa|Merci d'avoir vu sa soif.
 maman|Quelle couleur, Raphaël ?</t>
         </is>
@@ -2698,12 +2698,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>On attend les gouttes. Raphaël s'accroupit près du bac. Il penche l'arrosoir jaune, un tout petit peu. Une goutte tombe, puis une autre. Elle boit, tu vois ? La tête jaune se redresse un peu. Raphaël gigote, puis il se tient. Bravo, elle boit. Le robinet n'est plus qu'un murmure. Une abeille peut revenir.</t>
+          <t>On attend les gouttes. Raphaël s'accroupit près du bac. Il penche l'arrosoir jaune, un tout petit peu. Une goutte tombe, puis une autre. Elle boit, tu vois ? La tête jaune se redresse un peu. Raphaël gigote, puis il se tient. Bravo, elle boit. Le robinet fait à peine plic. Une abeille peut revenir.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>On attend les gouttes. Raphaël s'accroupit près du bac. Il penche l'arrosoir jaune, un tout petit peu. Une goutte tombe, puis une autre. Elle boit, tu vois ? La tête jaune se redresse un peu. Raphaël gigote, puis il se tient. Bravo, elle boit. Le robinet n'est plus qu'un murmure. Une abeille peut revenir.</t>
+          <t>On attend les gouttes. Raphaël s'accroupit près du bac. Il penche l'arrosoir jaune, un tout petit peu. Une goutte tombe, puis une autre. Elle boit, tu vois ? La tête jaune se redresse un peu. Raphaël gigote, puis il se tient. Bravo, elle boit. Le robinet fait à peine plic. Une abeille peut revenir.</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -2846,7 +2846,7 @@
 narrateur|La tête jaune se redresse un peu.
 narrateur|Raphaël gigote, puis il se tient.
 maman|Bravo, elle boit.
-narrateur|Le robinet n'est plus qu'un murmure.
+narrateur|Le robinet fait à peine plic.
 enfant-m|Une abeille peut revenir.</t>
         </is>
       </c>
@@ -2874,12 +2874,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>La tête jaune ne penche plus. Ils restent près du bac, sans bouger beaucoup. La marguerite a pris le temps. Tes gouttes sont arrivées. Ça sent encore la menthe, tout près. Une abeille passe, puis s'en va. Un grain de sable sèche sur le pétale jaune.</t>
+          <t>La tête jaune ne penche plus. Ils restent près du bac, sans bouger beaucoup. La marguerite a pris le temps. Tes gouttes sont arrivées. Le bac garde un rond d'ombre. Un grain de sable sèche sur le pétale jaune.</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>La tête jaune ne penche plus. Ils restent près du bac, sans bouger beaucoup. La marguerite a pris le temps. Tes gouttes sont arrivées. Ça sent encore la menthe, tout près. Une abeille passe, puis s'en va. Un grain de sable sèche sur le pétale jaune.</t>
+          <t>La tête jaune ne penche plus. Ils restent près du bac, sans bouger beaucoup. La marguerite a pris le temps. Tes gouttes sont arrivées. Le bac garde un rond d'ombre. Un grain de sable sèche sur le pétale jaune.</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3018,8 +3018,7 @@
 narrateur|Ils restent près du bac, sans bouger beaucoup.
 maman|La marguerite a pris le temps.
 papa|Tes gouttes sont arrivées.
-narrateur|Ça sent encore la menthe, tout près.
-narrateur|Une abeille passe, puis s'en va.
+narrateur|Le bac garde un rond d'ombre.
 narrateur|Un grain de sable sèche sur le pétale jaune.</t>
         </is>
       </c>
@@ -3223,12 +3222,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>La tête jaune ne penche plus. La petite tasse repose près du bac. Ta tasse a fait le voyage. Tu as couru, l'eau non. Ça sent encore la menthe, tout près. Une abeille passe, puis s'en va. La tasse garde un rond de soleil.</t>
+          <t>La tête jaune ne penche plus. La petite tasse repose près du bac. Ta tasse a fait le voyage. Tu as couru, l'eau non. La petite tasse se tait. La tasse garde un rond de soleil.</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>La tête jaune ne penche plus. La petite tasse repose près du bac. Ta tasse a fait le voyage. Tu as couru, l'eau non. Ça sent encore la menthe, tout près. Une abeille passe, puis s'en va. La tasse garde un rond de soleil.</t>
+          <t>La tête jaune ne penche plus. La petite tasse repose près du bac. Ta tasse a fait le voyage. Tu as couru, l'eau non. La petite tasse se tait. La tasse garde un rond de soleil.</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3367,8 +3366,7 @@
 narrateur|La petite tasse repose près du bac.
 maman|Ta tasse a fait le voyage.
 papa|Tu as couru, l'eau non.
-narrateur|Ça sent encore la menthe, tout près.
-narrateur|Une abeille passe, puis s'en va.
+narrateur|La petite tasse se tait.
 narrateur|La tasse garde un rond de soleil.</t>
         </is>
       </c>
@@ -3572,12 +3570,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>La tête jaune ne penche plus. Papa repose l'arrosoir jaune près du bac. Vous avez visé juste. À deux, c'était plus calme. Ça sent encore la menthe, tout près. Une abeille passe, puis s'en va. L'ombre de papa reste un moment sur le bac.</t>
+          <t>La tête jaune ne penche plus. Papa repose l'arrosoir jaune près du bac. Vous avez visé juste. À deux, c'était plus calme. Papa s'essuie les mains sur le linge rose. L'ombre de papa reste un moment sur le bac.</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>La tête jaune ne penche plus. Papa repose l'arrosoir jaune près du bac. Vous avez visé juste. À deux, c'était plus calme. Ça sent encore la menthe, tout près. Une abeille passe, puis s'en va. L'ombre de papa reste un moment sur le bac.</t>
+          <t>La tête jaune ne penche plus. Papa repose l'arrosoir jaune près du bac. Vous avez visé juste. À deux, c'était plus calme. Papa s'essuie les mains sur le linge rose. L'ombre de papa reste un moment sur le bac.</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -3716,8 +3714,7 @@
 narrateur|Papa repose l'arrosoir jaune près du bac.
 maman|Vous avez visé juste.
 papa|À deux, c'était plus calme.
-narrateur|Ça sent encore la menthe, tout près.
-narrateur|Une abeille passe, puis s'en va.
+narrateur|Papa s'essuie les mains sur le linge rose.
 narrateur|L'ombre de papa reste un moment sur le bac.</t>
         </is>
       </c>
@@ -4116,12 +4113,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>On attend les gouttes. Raphaël s'accroupit près du bac. Il penche l'arrosoir jaune, un tout petit peu. Une goutte tombe, puis une autre. Elle boit, tu vois ? La tête jaune se redresse un peu. Raphaël gigote, puis il se tient. Bravo, elle boit. Le seau n'est plus qu'un murmure. Une abeille peut revenir.</t>
+          <t>On attend les gouttes. Raphaël s'accroupit près du bac. Il penche l'arrosoir jaune, un tout petit peu. Une goutte tombe, puis une autre. Elle boit, tu vois ? La tête jaune se redresse un peu. Raphaël gigote, puis il se tient. Bravo, elle boit. Le seau fait à peine plic. Une abeille peut revenir.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>On attend les gouttes. Raphaël s'accroupit près du bac. Il penche l'arrosoir jaune, un tout petit peu. Une goutte tombe, puis une autre. Elle boit, tu vois ? La tête jaune se redresse un peu. Raphaël gigote, puis il se tient. Bravo, elle boit. Le seau n'est plus qu'un murmure. Une abeille peut revenir.</t>
+          <t>On attend les gouttes. Raphaël s'accroupit près du bac. Il penche l'arrosoir jaune, un tout petit peu. Une goutte tombe, puis une autre. Elle boit, tu vois ? La tête jaune se redresse un peu. Raphaël gigote, puis il se tient. Bravo, elle boit. Le seau fait à peine plic. Une abeille peut revenir.</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4264,7 +4261,7 @@
 narrateur|La tête jaune se redresse un peu.
 narrateur|Raphaël gigote, puis il se tient.
 maman|Bravo, elle boit.
-narrateur|Le seau n'est plus qu'un murmure.
+narrateur|Le seau fait à peine plic.
 enfant-m|Une abeille peut revenir.</t>
         </is>
       </c>
@@ -4292,12 +4289,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>La tête jaune ne penche plus. Ils restent près du bac, sans bouger beaucoup. La marguerite a pris le temps. Tes gouttes sont arrivées. Ça sent encore la menthe, tout près. Une abeille passe, puis s'en va. Le seau a un fond de sable, tout calme.</t>
+          <t>La tête jaune ne penche plus. Ils restent près du bac, sans bouger beaucoup. La marguerite a pris le temps. Tes gouttes sont arrivées. Le bac garde un rond d'ombre. Le seau a un fond de sable, tout calme.</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>La tête jaune ne penche plus. Ils restent près du bac, sans bouger beaucoup. La marguerite a pris le temps. Tes gouttes sont arrivées. Ça sent encore la menthe, tout près. Une abeille passe, puis s'en va. Le seau a un fond de sable, tout calme.</t>
+          <t>La tête jaune ne penche plus. Ils restent près du bac, sans bouger beaucoup. La marguerite a pris le temps. Tes gouttes sont arrivées. Le bac garde un rond d'ombre. Le seau a un fond de sable, tout calme.</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4436,8 +4433,7 @@
 narrateur|Ils restent près du bac, sans bouger beaucoup.
 maman|La marguerite a pris le temps.
 papa|Tes gouttes sont arrivées.
-narrateur|Ça sent encore la menthe, tout près.
-narrateur|Une abeille passe, puis s'en va.
+narrateur|Le bac garde un rond d'ombre.
 narrateur|Le seau a un fond de sable, tout calme.</t>
         </is>
       </c>
@@ -4641,12 +4637,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>La tête jaune ne penche plus. La petite tasse repose près du bac. Ta tasse a fait le voyage. Tu as couru, l'eau non. Ça sent encore la menthe, tout près. Une abeille passe, puis s'en va. Une miette de sable brille dans la tasse.</t>
+          <t>La tête jaune ne penche plus. La petite tasse repose près du bac. Ta tasse a fait le voyage. Tu as couru, l'eau non. La petite tasse se tait. Une miette de sable brille dans la tasse.</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>La tête jaune ne penche plus. La petite tasse repose près du bac. Ta tasse a fait le voyage. Tu as couru, l'eau non. Ça sent encore la menthe, tout près. Une abeille passe, puis s'en va. Une miette de sable brille dans la tasse.</t>
+          <t>La tête jaune ne penche plus. La petite tasse repose près du bac. Ta tasse a fait le voyage. Tu as couru, l'eau non. La petite tasse se tait. Une miette de sable brille dans la tasse.</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -4785,8 +4781,7 @@
 narrateur|La petite tasse repose près du bac.
 maman|Ta tasse a fait le voyage.
 papa|Tu as couru, l'eau non.
-narrateur|Ça sent encore la menthe, tout près.
-narrateur|Une abeille passe, puis s'en va.
+narrateur|La petite tasse se tait.
 narrateur|Une miette de sable brille dans la tasse.</t>
         </is>
       </c>
@@ -4990,12 +4985,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>La tête jaune ne penche plus. Papa repose l'arrosoir jaune près du bac. Vous avez visé juste. À deux, c'était plus calme. Ça sent encore la menthe, tout près. Une abeille passe, puis s'en va. Les orteils de Raphaël ont séché.</t>
+          <t>La tête jaune ne penche plus. Papa repose l'arrosoir jaune près du bac. Vous avez visé juste. À deux, c'était plus calme. Papa s'essuie les mains sur le linge rose. Les orteils de Raphaël ont séché.</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>La tête jaune ne penche plus. Papa repose l'arrosoir jaune près du bac. Vous avez visé juste. À deux, c'était plus calme. Ça sent encore la menthe, tout près. Une abeille passe, puis s'en va. Les orteils de Raphaël ont séché.</t>
+          <t>La tête jaune ne penche plus. Papa repose l'arrosoir jaune près du bac. Vous avez visé juste. À deux, c'était plus calme. Papa s'essuie les mains sur le linge rose. Les orteils de Raphaël ont séché.</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5134,8 +5129,7 @@
 narrateur|Papa repose l'arrosoir jaune près du bac.
 maman|Vous avez visé juste.
 papa|À deux, c'était plus calme.
-narrateur|Ça sent encore la menthe, tout près.
-narrateur|Une abeille passe, puis s'en va.
+narrateur|Papa s'essuie les mains sur le linge rose.
 narrateur|Les orteils de Raphaël ont séché.</t>
         </is>
       </c>
@@ -5534,12 +5528,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>On attend les gouttes. Raphaël s'accroupit près du bac. Il penche l'arrosoir jaune, un tout petit peu. Une goutte tombe, puis une autre. Elle boit, tu vois ? La tête jaune se redresse un peu. Raphaël gigote, puis il se tient. Bravo, elle boit. L'arrosoir n'est plus qu'un murmure. Une abeille peut revenir.</t>
+          <t>On attend les gouttes. Raphaël s'accroupit près du bac. Il penche l'arrosoir jaune, un tout petit peu. Une goutte tombe, puis une autre. Elle boit, tu vois ? La tête jaune se redresse un peu. Raphaël gigote, puis il se tient. Bravo, elle boit. L'arrosoir fait à peine plic. Une abeille peut revenir.</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>On attend les gouttes. Raphaël s'accroupit près du bac. Il penche l'arrosoir jaune, un tout petit peu. Une goutte tombe, puis une autre. Elle boit, tu vois ? La tête jaune se redresse un peu. Raphaël gigote, puis il se tient. Bravo, elle boit. L'arrosoir n'est plus qu'un murmure. Une abeille peut revenir.</t>
+          <t>On attend les gouttes. Raphaël s'accroupit près du bac. Il penche l'arrosoir jaune, un tout petit peu. Une goutte tombe, puis une autre. Elle boit, tu vois ? La tête jaune se redresse un peu. Raphaël gigote, puis il se tient. Bravo, elle boit. L'arrosoir fait à peine plic. Une abeille peut revenir.</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -5682,7 +5676,7 @@
 narrateur|La tête jaune se redresse un peu.
 narrateur|Raphaël gigote, puis il se tient.
 maman|Bravo, elle boit.
-narrateur|L'arrosoir n'est plus qu'un murmure.
+narrateur|L'arrosoir fait à peine plic.
 enfant-m|Une abeille peut revenir.</t>
         </is>
       </c>
@@ -5710,12 +5704,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>La tête jaune ne penche plus. Ils restent près du bac, sans bouger beaucoup. La marguerite a pris le temps. Tes gouttes sont arrivées. Ça sent encore la menthe, tout près. Une abeille passe, puis s'en va. L'abeille est revenue, tout près.</t>
+          <t>La tête jaune ne penche plus. Ils restent près du bac, sans bouger beaucoup. La marguerite a pris le temps. Tes gouttes sont arrivées. Le bac garde un rond d'ombre. L'abeille est revenue, tout près.</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>La tête jaune ne penche plus. Ils restent près du bac, sans bouger beaucoup. La marguerite a pris le temps. Tes gouttes sont arrivées. Ça sent encore la menthe, tout près. Une abeille passe, puis s'en va. L'abeille est revenue, tout près.</t>
+          <t>La tête jaune ne penche plus. Ils restent près du bac, sans bouger beaucoup. La marguerite a pris le temps. Tes gouttes sont arrivées. Le bac garde un rond d'ombre. L'abeille est revenue, tout près.</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -5854,8 +5848,7 @@
 narrateur|Ils restent près du bac, sans bouger beaucoup.
 maman|La marguerite a pris le temps.
 papa|Tes gouttes sont arrivées.
-narrateur|Ça sent encore la menthe, tout près.
-narrateur|Une abeille passe, puis s'en va.
+narrateur|Le bac garde un rond d'ombre.
 narrateur|L'abeille est revenue, tout près.</t>
         </is>
       </c>
@@ -6059,12 +6052,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>La tête jaune ne penche plus. La petite tasse repose près du bac. Ta tasse a fait le voyage. Tu as couru, l'eau non. Ça sent encore la menthe, tout près. Une abeille passe, puis s'en va. La dernière goutte de maman a voyagé.</t>
+          <t>La tête jaune ne penche plus. La petite tasse repose près du bac. Ta tasse a fait le voyage. Tu as couru, l'eau non. La petite tasse se tait. La dernière goutte de maman a voyagé.</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>La tête jaune ne penche plus. La petite tasse repose près du bac. Ta tasse a fait le voyage. Tu as couru, l'eau non. Ça sent encore la menthe, tout près. Une abeille passe, puis s'en va. La dernière goutte de maman a voyagé.</t>
+          <t>La tête jaune ne penche plus. La petite tasse repose près du bac. Ta tasse a fait le voyage. Tu as couru, l'eau non. La petite tasse se tait. La dernière goutte de maman a voyagé.</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6203,8 +6196,7 @@
 narrateur|La petite tasse repose près du bac.
 maman|Ta tasse a fait le voyage.
 papa|Tu as couru, l'eau non.
-narrateur|Ça sent encore la menthe, tout près.
-narrateur|Une abeille passe, puis s'en va.
+narrateur|La petite tasse se tait.
 narrateur|La dernière goutte de maman a voyagé.</t>
         </is>
       </c>
@@ -6408,12 +6400,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>La tête jaune ne penche plus. Papa repose l'arrosoir jaune près du bac. Vous avez visé juste. À deux, c'était plus calme. Ça sent encore la menthe, tout près. Une abeille passe, puis s'en va. Le bec de l'arrosoir ne gicle plus.</t>
+          <t>La tête jaune ne penche plus. Papa repose l'arrosoir jaune près du bac. Vous avez visé juste. À deux, c'était plus calme. Papa s'essuie les mains sur le linge rose. Le bec de l'arrosoir ne gicle plus.</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>La tête jaune ne penche plus. Papa repose l'arrosoir jaune près du bac. Vous avez visé juste. À deux, c'était plus calme. Ça sent encore la menthe, tout près. Une abeille passe, puis s'en va. Le bec de l'arrosoir ne gicle plus.</t>
+          <t>La tête jaune ne penche plus. Papa repose l'arrosoir jaune près du bac. Vous avez visé juste. À deux, c'était plus calme. Papa s'essuie les mains sur le linge rose. Le bec de l'arrosoir ne gicle plus.</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -6552,8 +6544,7 @@
 narrateur|Papa repose l'arrosoir jaune près du bac.
 maman|Vous avez visé juste.
 papa|À deux, c'était plus calme.
-narrateur|Ça sent encore la menthe, tout près.
-narrateur|Une abeille passe, puis s'en va.
+narrateur|Papa s'essuie les mains sur le linge rose.
 narrateur|Le bec de l'arrosoir ne gicle plus.</t>
         </is>
       </c>
@@ -7685,12 +7676,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>On attend les gouttes. Raphaël s'accroupit près des tomates. Il penche l'arrosoir rouge, un tout petit peu. Une goutte tombe, puis une autre. Elle boit, tu vois ? La tête rouge se redresse un peu. Raphaël gigote, puis il se tient. Bravo, elle boit. Le robinet n'est plus qu'un murmure. Une coccinelle peut revenir.</t>
+          <t>On attend les gouttes. Raphaël s'accroupit près des tomates. Il penche l'arrosoir rouge, un tout petit peu. Une goutte tombe, puis une autre. Elle boit, tu vois ? La tête rouge se redresse un peu. Raphaël gigote, puis il se tient. Bravo, elle boit. Le robinet fait à peine plic. Une coccinelle peut revenir.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>On attend les gouttes. Raphaël s'accroupit près des tomates. Il penche l'arrosoir rouge, un tout petit peu. Une goutte tombe, puis une autre. Elle boit, tu vois ? La tête rouge se redresse un peu. Raphaël gigote, puis il se tient. Bravo, elle boit. Le robinet n'est plus qu'un murmure. Une coccinelle peut revenir.</t>
+          <t>On attend les gouttes. Raphaël s'accroupit près des tomates. Il penche l'arrosoir rouge, un tout petit peu. Une goutte tombe, puis une autre. Elle boit, tu vois ? La tête rouge se redresse un peu. Raphaël gigote, puis il se tient. Bravo, elle boit. Le robinet fait à peine plic. Une coccinelle peut revenir.</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -7833,7 +7824,7 @@
 narrateur|La tête rouge se redresse un peu.
 narrateur|Raphaël gigote, puis il se tient.
 maman|Bravo, elle boit.
-narrateur|Le robinet n'est plus qu'un murmure.
+narrateur|Le robinet fait à peine plic.
 enfant-m|Une coccinelle peut revenir.</t>
         </is>
       </c>
@@ -7861,12 +7852,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>La tête rouge ne penche plus. Ils restent près des tomates, sans bouger beaucoup. Le coquelicot a pris le temps. Tes gouttes sont arrivées. Ça sent encore la menthe, tout près. Une coccinelle passe, puis s'en va. Une coccinelle s'est posée sur le bouton rouge.</t>
+          <t>La tête rouge ne penche plus. Ils restent près des tomates, sans bouger beaucoup. Le coquelicot a pris le temps. Tes gouttes sont arrivées. Une tomate encore chaude brille à côté. Une coccinelle s'est posée sur le bouton rouge.</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>La tête rouge ne penche plus. Ils restent près des tomates, sans bouger beaucoup. Le coquelicot a pris le temps. Tes gouttes sont arrivées. Ça sent encore la menthe, tout près. Une coccinelle passe, puis s'en va. Une coccinelle s'est posée sur le bouton rouge.</t>
+          <t>La tête rouge ne penche plus. Ils restent près des tomates, sans bouger beaucoup. Le coquelicot a pris le temps. Tes gouttes sont arrivées. Une tomate encore chaude brille à côté. Une coccinelle s'est posée sur le bouton rouge.</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -8005,8 +7996,7 @@
 narrateur|Ils restent près des tomates, sans bouger beaucoup.
 maman|Le coquelicot a pris le temps.
 papa|Tes gouttes sont arrivées.
-narrateur|Ça sent encore la menthe, tout près.
-narrateur|Une coccinelle passe, puis s'en va.
+narrateur|Une tomate encore chaude brille à côté.
 narrateur|Une coccinelle s'est posée sur le bouton rouge.</t>
         </is>
       </c>
@@ -8210,12 +8200,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>La tête rouge ne penche plus. La petite tasse repose près des tomates. Ta tasse a fait le voyage. Tu as couru, l'eau non. Ça sent encore la menthe, tout près. Une coccinelle passe, puis s'en va. Une tomate a une goutte, pour de rire.</t>
+          <t>La tête rouge ne penche plus. La petite tasse repose près des tomates. Ta tasse a fait le voyage. Tu as couru, l'eau non. La terre a un petit sourire mouillé. Une tomate a une goutte, pour de rire.</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>La tête rouge ne penche plus. La petite tasse repose près des tomates. Ta tasse a fait le voyage. Tu as couru, l'eau non. Ça sent encore la menthe, tout près. Une coccinelle passe, puis s'en va. Une tomate a une goutte, pour de rire.</t>
+          <t>La tête rouge ne penche plus. La petite tasse repose près des tomates. Ta tasse a fait le voyage. Tu as couru, l'eau non. La terre a un petit sourire mouillé. Une tomate a une goutte, pour de rire.</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -8354,8 +8344,7 @@
 narrateur|La petite tasse repose près des tomates.
 maman|Ta tasse a fait le voyage.
 papa|Tu as couru, l'eau non.
-narrateur|Ça sent encore la menthe, tout près.
-narrateur|Une coccinelle passe, puis s'en va.
+narrateur|La terre a un petit sourire mouillé.
 narrateur|Une tomate a une goutte, pour de rire.</t>
         </is>
       </c>
@@ -8559,12 +8548,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>La tête rouge ne penche plus. Papa repose l'arrosoir rouge près des tomates. Vous avez visé juste. À deux, c'était plus calme. Ça sent encore la menthe, tout près. Une coccinelle passe, puis s'en va. Le filet du robinet s'est tu.</t>
+          <t>La tête rouge ne penche plus. Papa repose l'arrosoir rouge près des tomates. Vous avez visé juste. À deux, c'était plus calme. Les plants de tomates ne bougent plus. Le filet du robinet s'est tu.</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>La tête rouge ne penche plus. Papa repose l'arrosoir rouge près des tomates. Vous avez visé juste. À deux, c'était plus calme. Ça sent encore la menthe, tout près. Une coccinelle passe, puis s'en va. Le filet du robinet s'est tu.</t>
+          <t>La tête rouge ne penche plus. Papa repose l'arrosoir rouge près des tomates. Vous avez visé juste. À deux, c'était plus calme. Les plants de tomates ne bougent plus. Le filet du robinet s'est tu.</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -8703,8 +8692,7 @@
 narrateur|Papa repose l'arrosoir rouge près des tomates.
 maman|Vous avez visé juste.
 papa|À deux, c'était plus calme.
-narrateur|Ça sent encore la menthe, tout près.
-narrateur|Une coccinelle passe, puis s'en va.
+narrateur|Les plants de tomates ne bougent plus.
 narrateur|Le filet du robinet s'est tu.</t>
         </is>
       </c>
@@ -9102,12 +9090,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>On attend les gouttes. Raphaël s'accroupit près des tomates. Il penche l'arrosoir rouge, un tout petit peu. Une goutte tombe, puis une autre. Elle boit, tu vois ? La tête rouge se redresse un peu. Raphaël gigote, puis il se tient. Bravo, elle boit. Le seau n'est plus qu'un murmure. Une coccinelle peut revenir.</t>
+          <t>On attend les gouttes. Raphaël s'accroupit près des tomates. Il penche l'arrosoir rouge, un tout petit peu. Une goutte tombe, puis une autre. Elle boit, tu vois ? La tête rouge se redresse un peu. Raphaël gigote, puis il se tient. Bravo, elle boit. Le seau fait à peine plic. Une coccinelle peut revenir.</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>On attend les gouttes. Raphaël s'accroupit près des tomates. Il penche l'arrosoir rouge, un tout petit peu. Une goutte tombe, puis une autre. Elle boit, tu vois ? La tête rouge se redresse un peu. Raphaël gigote, puis il se tient. Bravo, elle boit. Le seau n'est plus qu'un murmure. Une coccinelle peut revenir.</t>
+          <t>On attend les gouttes. Raphaël s'accroupit près des tomates. Il penche l'arrosoir rouge, un tout petit peu. Une goutte tombe, puis une autre. Elle boit, tu vois ? La tête rouge se redresse un peu. Raphaël gigote, puis il se tient. Bravo, elle boit. Le seau fait à peine plic. Une coccinelle peut revenir.</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -9250,7 +9238,7 @@
 narrateur|La tête rouge se redresse un peu.
 narrateur|Raphaël gigote, puis il se tient.
 maman|Bravo, elle boit.
-narrateur|Le seau n'est plus qu'un murmure.
+narrateur|Le seau fait à peine plic.
 enfant-m|Une coccinelle peut revenir.</t>
         </is>
       </c>
@@ -9278,12 +9266,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>La tête rouge ne penche plus. Ils restent près des tomates, sans bouger beaucoup. Le coquelicot a pris le temps. Tes gouttes sont arrivées. Ça sent encore la menthe, tout près. Une coccinelle passe, puis s'en va. La terre a cessé de faire des bulles.</t>
+          <t>La tête rouge ne penche plus. Ils restent près des tomates, sans bouger beaucoup. Le coquelicot a pris le temps. Tes gouttes sont arrivées. Une tomate encore chaude brille à côté. La terre a cessé de faire des bulles.</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>La tête rouge ne penche plus. Ils restent près des tomates, sans bouger beaucoup. Le coquelicot a pris le temps. Tes gouttes sont arrivées. Ça sent encore la menthe, tout près. Une coccinelle passe, puis s'en va. La terre a cessé de faire des bulles.</t>
+          <t>La tête rouge ne penche plus. Ils restent près des tomates, sans bouger beaucoup. Le coquelicot a pris le temps. Tes gouttes sont arrivées. Une tomate encore chaude brille à côté. La terre a cessé de faire des bulles.</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -9422,8 +9410,7 @@
 narrateur|Ils restent près des tomates, sans bouger beaucoup.
 maman|Le coquelicot a pris le temps.
 papa|Tes gouttes sont arrivées.
-narrateur|Ça sent encore la menthe, tout près.
-narrateur|Une coccinelle passe, puis s'en va.
+narrateur|Une tomate encore chaude brille à côté.
 narrateur|La terre a cessé de faire des bulles.</t>
         </is>
       </c>
@@ -9627,12 +9614,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>La tête rouge ne penche plus. La petite tasse repose près des tomates. Ta tasse a fait le voyage. Tu as couru, l'eau non. Ça sent encore la menthe, tout près. Une coccinelle passe, puis s'en va. La tasse a une auréole de terre.</t>
+          <t>La tête rouge ne penche plus. La petite tasse repose près des tomates. Ta tasse a fait le voyage. Tu as couru, l'eau non. La terre a un petit sourire mouillé. La tasse a une auréole de terre.</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>La tête rouge ne penche plus. La petite tasse repose près des tomates. Ta tasse a fait le voyage. Tu as couru, l'eau non. Ça sent encore la menthe, tout près. Une coccinelle passe, puis s'en va. La tasse a une auréole de terre.</t>
+          <t>La tête rouge ne penche plus. La petite tasse repose près des tomates. Ta tasse a fait le voyage. Tu as couru, l'eau non. La terre a un petit sourire mouillé. La tasse a une auréole de terre.</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -9771,8 +9758,7 @@
 narrateur|La petite tasse repose près des tomates.
 maman|Ta tasse a fait le voyage.
 papa|Tu as couru, l'eau non.
-narrateur|Ça sent encore la menthe, tout près.
-narrateur|Une coccinelle passe, puis s'en va.
+narrateur|La terre a un petit sourire mouillé.
 narrateur|La tasse a une auréole de terre.</t>
         </is>
       </c>
@@ -9976,12 +9962,12 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>La tête rouge ne penche plus. Papa repose l'arrosoir rouge près des tomates. Vous avez visé juste. À deux, c'était plus calme. Ça sent encore la menthe, tout près. Une coccinelle passe, puis s'en va. Le seau repose entre les tomates.</t>
+          <t>La tête rouge ne penche plus. Papa repose l'arrosoir rouge près des tomates. Vous avez visé juste. À deux, c'était plus calme. Les plants de tomates ne bougent plus. Le seau repose entre les tomates.</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>La tête rouge ne penche plus. Papa repose l'arrosoir rouge près des tomates. Vous avez visé juste. À deux, c'était plus calme. Ça sent encore la menthe, tout près. Une coccinelle passe, puis s'en va. Le seau repose entre les tomates.</t>
+          <t>La tête rouge ne penche plus. Papa repose l'arrosoir rouge près des tomates. Vous avez visé juste. À deux, c'était plus calme. Les plants de tomates ne bougent plus. Le seau repose entre les tomates.</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -10120,8 +10106,7 @@
 narrateur|Papa repose l'arrosoir rouge près des tomates.
 maman|Vous avez visé juste.
 papa|À deux, c'était plus calme.
-narrateur|Ça sent encore la menthe, tout près.
-narrateur|Une coccinelle passe, puis s'en va.
+narrateur|Les plants de tomates ne bougent plus.
 narrateur|Le seau repose entre les tomates.</t>
         </is>
       </c>
@@ -10520,12 +10505,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>On attend les gouttes. Raphaël s'accroupit près des tomates. Il penche l'arrosoir rouge, un tout petit peu. Une goutte tombe, puis une autre. Elle boit, tu vois ? La tête rouge se redresse un peu. Raphaël gigote, puis il se tient. Bravo, elle boit. L'arrosoir n'est plus qu'un murmure. Une coccinelle peut revenir.</t>
+          <t>On attend les gouttes. Raphaël s'accroupit près des tomates. Il penche l'arrosoir rouge, un tout petit peu. Une goutte tombe, puis une autre. Elle boit, tu vois ? La tête rouge se redresse un peu. Raphaël gigote, puis il se tient. Bravo, elle boit. L'arrosoir fait à peine plic. Une coccinelle peut revenir.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>On attend les gouttes. Raphaël s'accroupit près des tomates. Il penche l'arrosoir rouge, un tout petit peu. Une goutte tombe, puis une autre. Elle boit, tu vois ? La tête rouge se redresse un peu. Raphaël gigote, puis il se tient. Bravo, elle boit. L'arrosoir n'est plus qu'un murmure. Une coccinelle peut revenir.</t>
+          <t>On attend les gouttes. Raphaël s'accroupit près des tomates. Il penche l'arrosoir rouge, un tout petit peu. Une goutte tombe, puis une autre. Elle boit, tu vois ? La tête rouge se redresse un peu. Raphaël gigote, puis il se tient. Bravo, elle boit. L'arrosoir fait à peine plic. Une coccinelle peut revenir.</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -10668,7 +10653,7 @@
 narrateur|La tête rouge se redresse un peu.
 narrateur|Raphaël gigote, puis il se tient.
 maman|Bravo, elle boit.
-narrateur|L'arrosoir n'est plus qu'un murmure.
+narrateur|L'arrosoir fait à peine plic.
 enfant-m|Une coccinelle peut revenir.</t>
         </is>
       </c>
@@ -10696,12 +10681,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>La tête rouge ne penche plus. Ils restent près des tomates, sans bouger beaucoup. Le coquelicot a pris le temps. Tes gouttes sont arrivées. Ça sent encore la menthe, tout près. Une coccinelle passe, puis s'en va. Un pétale rouge a gardé une goutte ronde.</t>
+          <t>La tête rouge ne penche plus. Ils restent près des tomates, sans bouger beaucoup. Le coquelicot a pris le temps. Tes gouttes sont arrivées. Une tomate encore chaude brille à côté. Un pétale rouge a gardé une goutte ronde.</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>La tête rouge ne penche plus. Ils restent près des tomates, sans bouger beaucoup. Le coquelicot a pris le temps. Tes gouttes sont arrivées. Ça sent encore la menthe, tout près. Une coccinelle passe, puis s'en va. Un pétale rouge a gardé une goutte ronde.</t>
+          <t>La tête rouge ne penche plus. Ils restent près des tomates, sans bouger beaucoup. Le coquelicot a pris le temps. Tes gouttes sont arrivées. Une tomate encore chaude brille à côté. Un pétale rouge a gardé une goutte ronde.</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -10840,8 +10825,7 @@
 narrateur|Ils restent près des tomates, sans bouger beaucoup.
 maman|Le coquelicot a pris le temps.
 papa|Tes gouttes sont arrivées.
-narrateur|Ça sent encore la menthe, tout près.
-narrateur|Une coccinelle passe, puis s'en va.
+narrateur|Une tomate encore chaude brille à côté.
 narrateur|Un pétale rouge a gardé une goutte ronde.</t>
         </is>
       </c>
@@ -11045,12 +11029,12 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>La tête rouge ne penche plus. La petite tasse repose près des tomates. Ta tasse a fait le voyage. Tu as couru, l'eau non. Ça sent encore la menthe, tout près. Une coccinelle passe, puis s'en va. La coccinelle a repris le bec, tout doux.</t>
+          <t>La tête rouge ne penche plus. La petite tasse repose près des tomates. Ta tasse a fait le voyage. Tu as couru, l'eau non. La terre a un petit sourire mouillé. La coccinelle a repris le bec, tout doux.</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>La tête rouge ne penche plus. La petite tasse repose près des tomates. Ta tasse a fait le voyage. Tu as couru, l'eau non. Ça sent encore la menthe, tout près. Une coccinelle passe, puis s'en va. La coccinelle a repris le bec, tout doux.</t>
+          <t>La tête rouge ne penche plus. La petite tasse repose près des tomates. Ta tasse a fait le voyage. Tu as couru, l'eau non. La terre a un petit sourire mouillé. La coccinelle a repris le bec, tout doux.</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -11189,8 +11173,7 @@
 narrateur|La petite tasse repose près des tomates.
 maman|Ta tasse a fait le voyage.
 papa|Tu as couru, l'eau non.
-narrateur|Ça sent encore la menthe, tout près.
-narrateur|Une coccinelle passe, puis s'en va.
+narrateur|La terre a un petit sourire mouillé.
 narrateur|La coccinelle a repris le bec, tout doux.</t>
         </is>
       </c>
@@ -11394,12 +11377,12 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>La tête rouge ne penche plus. Papa repose l'arrosoir rouge près des tomates. Vous avez visé juste. À deux, c'était plus calme. Ça sent encore la menthe, tout près. Une coccinelle passe, puis s'en va. L'arrosoir de maman s'est assis dans l'herbe.</t>
+          <t>La tête rouge ne penche plus. Papa repose l'arrosoir rouge près des tomates. Vous avez visé juste. À deux, c'était plus calme. Les plants de tomates ne bougent plus. L'arrosoir de maman s'est assis dans l'herbe.</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>La tête rouge ne penche plus. Papa repose l'arrosoir rouge près des tomates. Vous avez visé juste. À deux, c'était plus calme. Ça sent encore la menthe, tout près. Une coccinelle passe, puis s'en va. L'arrosoir de maman s'est assis dans l'herbe.</t>
+          <t>La tête rouge ne penche plus. Papa repose l'arrosoir rouge près des tomates. Vous avez visé juste. À deux, c'était plus calme. Les plants de tomates ne bougent plus. L'arrosoir de maman s'est assis dans l'herbe.</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -11538,8 +11521,7 @@
 narrateur|Papa repose l'arrosoir rouge près des tomates.
 maman|Vous avez visé juste.
 papa|À deux, c'était plus calme.
-narrateur|Ça sent encore la menthe, tout près.
-narrateur|Une coccinelle passe, puis s'en va.
+narrateur|Les plants de tomates ne bougent plus.
 narrateur|L'arrosoir de maman s'est assis dans l'herbe.</t>
         </is>
       </c>
@@ -12671,12 +12653,12 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>On attend les gouttes. Raphaël s'accroupit près du banc. Il penche l'arrosoir bleu, un tout petit peu. Une goutte tombe, puis une autre. Elle boit, tu vois ? La tête bleue se redresse un peu. Raphaël gigote, puis il se tient. Bravo, elle boit. Le robinet n'est plus qu'un murmure. Un papillon peut revenir.</t>
+          <t>On attend les gouttes. Raphaël s'accroupit près du banc. Il penche l'arrosoir bleu, un tout petit peu. Une goutte tombe, puis une autre. Elle boit, tu vois ? La tête bleue se redresse un peu. Raphaël gigote, puis il se tient. Bravo, elle boit. Le robinet fait à peine plic. Un papillon peut revenir.</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>On attend les gouttes. Raphaël s'accroupit près du banc. Il penche l'arrosoir bleu, un tout petit peu. Une goutte tombe, puis une autre. Elle boit, tu vois ? La tête bleue se redresse un peu. Raphaël gigote, puis il se tient. Bravo, elle boit. Le robinet n'est plus qu'un murmure. Un papillon peut revenir.</t>
+          <t>On attend les gouttes. Raphaël s'accroupit près du banc. Il penche l'arrosoir bleu, un tout petit peu. Une goutte tombe, puis une autre. Elle boit, tu vois ? La tête bleue se redresse un peu. Raphaël gigote, puis il se tient. Bravo, elle boit. Le robinet fait à peine plic. Un papillon peut revenir.</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -12819,7 +12801,7 @@
 narrateur|La tête bleue se redresse un peu.
 narrateur|Raphaël gigote, puis il se tient.
 maman|Bravo, elle boit.
-narrateur|Le robinet n'est plus qu'un murmure.
+narrateur|Le robinet fait à peine plic.
 enfant-m|Un papillon peut revenir.</t>
         </is>
       </c>
@@ -12847,12 +12829,12 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>La tête bleue ne penche plus. Ils restent près du banc, sans bouger beaucoup. La fleur bleue a pris le temps. Tes gouttes sont arrivées. Ça sent encore la menthe, tout près. Un papillon passe, puis s'en va. Le zinc du robinet a une perle froide.</t>
+          <t>La tête bleue ne penche plus. Ils restent près du banc, sans bouger beaucoup. La fleur bleue a pris le temps. Tes gouttes sont arrivées. Une perle d'eau reste dans l'ombre. Le zinc du robinet a une perle froide.</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>La tête bleue ne penche plus. Ils restent près du banc, sans bouger beaucoup. La fleur bleue a pris le temps. Tes gouttes sont arrivées. Ça sent encore la menthe, tout près. Un papillon passe, puis s'en va. Le zinc du robinet a une perle froide.</t>
+          <t>La tête bleue ne penche plus. Ils restent près du banc, sans bouger beaucoup. La fleur bleue a pris le temps. Tes gouttes sont arrivées. Une perle d'eau reste dans l'ombre. Le zinc du robinet a une perle froide.</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -12991,8 +12973,7 @@
 narrateur|Ils restent près du banc, sans bouger beaucoup.
 maman|La fleur bleue a pris le temps.
 papa|Tes gouttes sont arrivées.
-narrateur|Ça sent encore la menthe, tout près.
-narrateur|Un papillon passe, puis s'en va.
+narrateur|Une perle d'eau reste dans l'ombre.
 narrateur|Le zinc du robinet a une perle froide.</t>
         </is>
       </c>
@@ -13196,12 +13177,12 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>La tête bleue ne penche plus. La petite tasse repose près du banc. Ta tasse a fait le voyage. Tu as couru, l'eau non. Ça sent encore la menthe, tout près. Un papillon passe, puis s'en va. Le bois du banc a un petit nuage mouillé.</t>
+          <t>La tête bleue ne penche plus. La petite tasse repose près du banc. Ta tasse a fait le voyage. Tu as couru, l'eau non. Le bois sent encore la pluie d'hier. Le bois du banc a un petit nuage mouillé.</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>La tête bleue ne penche plus. La petite tasse repose près du banc. Ta tasse a fait le voyage. Tu as couru, l'eau non. Ça sent encore la menthe, tout près. Un papillon passe, puis s'en va. Le bois du banc a un petit nuage mouillé.</t>
+          <t>La tête bleue ne penche plus. La petite tasse repose près du banc. Ta tasse a fait le voyage. Tu as couru, l'eau non. Le bois sent encore la pluie d'hier. Le bois du banc a un petit nuage mouillé.</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -13340,8 +13321,7 @@
 narrateur|La petite tasse repose près du banc.
 maman|Ta tasse a fait le voyage.
 papa|Tu as couru, l'eau non.
-narrateur|Ça sent encore la menthe, tout près.
-narrateur|Un papillon passe, puis s'en va.
+narrateur|Le bois sent encore la pluie d'hier.
 narrateur|Le bois du banc a un petit nuage mouillé.</t>
         </is>
       </c>
@@ -13545,12 +13525,12 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>La tête bleue ne penche plus. Papa repose l'arrosoir bleu près du banc. Vous avez visé juste. À deux, c'était plus calme. Ça sent encore la menthe, tout près. Un papillon passe, puis s'en va. Un papillon est resté sur l'anse bleue.</t>
+          <t>La tête bleue ne penche plus. Papa repose l'arrosoir bleu près du banc. Vous avez visé juste. À deux, c'était plus calme. L'ombre du banc a reculé d'un pas. Un papillon est resté sur l'anse bleue.</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>La tête bleue ne penche plus. Papa repose l'arrosoir bleu près du banc. Vous avez visé juste. À deux, c'était plus calme. Ça sent encore la menthe, tout près. Un papillon passe, puis s'en va. Un papillon est resté sur l'anse bleue.</t>
+          <t>La tête bleue ne penche plus. Papa repose l'arrosoir bleu près du banc. Vous avez visé juste. À deux, c'était plus calme. L'ombre du banc a reculé d'un pas. Un papillon est resté sur l'anse bleue.</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
@@ -13689,8 +13669,7 @@
 narrateur|Papa repose l'arrosoir bleu près du banc.
 maman|Vous avez visé juste.
 papa|À deux, c'était plus calme.
-narrateur|Ça sent encore la menthe, tout près.
-narrateur|Un papillon passe, puis s'en va.
+narrateur|L'ombre du banc a reculé d'un pas.
 narrateur|Un papillon est resté sur l'anse bleue.</t>
         </is>
       </c>
@@ -14089,12 +14068,12 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>On attend les gouttes. Raphaël s'accroupit près du banc. Il penche l'arrosoir bleu, un tout petit peu. Une goutte tombe, puis une autre. Elle boit, tu vois ? La tête bleue se redresse un peu. Raphaël gigote, puis il se tient. Bravo, elle boit. Le seau n'est plus qu'un murmure. Un papillon peut revenir.</t>
+          <t>On attend les gouttes. Raphaël s'accroupit près du banc. Il penche l'arrosoir bleu, un tout petit peu. Une goutte tombe, puis une autre. Elle boit, tu vois ? La tête bleue se redresse un peu. Raphaël gigote, puis il se tient. Bravo, elle boit. Le seau fait à peine plic. Un papillon peut revenir.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>On attend les gouttes. Raphaël s'accroupit près du banc. Il penche l'arrosoir bleu, un tout petit peu. Une goutte tombe, puis une autre. Elle boit, tu vois ? La tête bleue se redresse un peu. Raphaël gigote, puis il se tient. Bravo, elle boit. Le seau n'est plus qu'un murmure. Un papillon peut revenir.</t>
+          <t>On attend les gouttes. Raphaël s'accroupit près du banc. Il penche l'arrosoir bleu, un tout petit peu. Une goutte tombe, puis une autre. Elle boit, tu vois ? La tête bleue se redresse un peu. Raphaël gigote, puis il se tient. Bravo, elle boit. Le seau fait à peine plic. Un papillon peut revenir.</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -14237,7 +14216,7 @@
 narrateur|La tête bleue se redresse un peu.
 narrateur|Raphaël gigote, puis il se tient.
 maman|Bravo, elle boit.
-narrateur|Le seau n'est plus qu'un murmure.
+narrateur|Le seau fait à peine plic.
 enfant-m|Un papillon peut revenir.</t>
         </is>
       </c>
@@ -14265,12 +14244,12 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>La tête bleue ne penche plus. Ils restent près du banc, sans bouger beaucoup. La fleur bleue a pris le temps. Tes gouttes sont arrivées. Ça sent encore la menthe, tout près. Un papillon passe, puis s'en va. L'ombre du seau a reculé, tout lent.</t>
+          <t>La tête bleue ne penche plus. Ils restent près du banc, sans bouger beaucoup. La fleur bleue a pris le temps. Tes gouttes sont arrivées. Une perle d'eau reste dans l'ombre. L'ombre du seau a reculé, tout lent.</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>La tête bleue ne penche plus. Ils restent près du banc, sans bouger beaucoup. La fleur bleue a pris le temps. Tes gouttes sont arrivées. Ça sent encore la menthe, tout près. Un papillon passe, puis s'en va. L'ombre du seau a reculé, tout lent.</t>
+          <t>La tête bleue ne penche plus. Ils restent près du banc, sans bouger beaucoup. La fleur bleue a pris le temps. Tes gouttes sont arrivées. Une perle d'eau reste dans l'ombre. L'ombre du seau a reculé, tout lent.</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
@@ -14409,8 +14388,7 @@
 narrateur|Ils restent près du banc, sans bouger beaucoup.
 maman|La fleur bleue a pris le temps.
 papa|Tes gouttes sont arrivées.
-narrateur|Ça sent encore la menthe, tout près.
-narrateur|Un papillon passe, puis s'en va.
+narrateur|Une perle d'eau reste dans l'ombre.
 narrateur|L'ombre du seau a reculé, tout lent.</t>
         </is>
       </c>
@@ -14614,12 +14592,12 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>La tête bleue ne penche plus. La petite tasse repose près du banc. Ta tasse a fait le voyage. Tu as couru, l'eau non. Ça sent encore la menthe, tout près. Un papillon passe, puis s'en va. La tasse cliquette une dernière fois.</t>
+          <t>La tête bleue ne penche plus. La petite tasse repose près du banc. Ta tasse a fait le voyage. Tu as couru, l'eau non. Le bois sent encore la pluie d'hier. La tasse cliquette une dernière fois.</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>La tête bleue ne penche plus. La petite tasse repose près du banc. Ta tasse a fait le voyage. Tu as couru, l'eau non. Ça sent encore la menthe, tout près. Un papillon passe, puis s'en va. La tasse cliquette une dernière fois.</t>
+          <t>La tête bleue ne penche plus. La petite tasse repose près du banc. Ta tasse a fait le voyage. Tu as couru, l'eau non. Le bois sent encore la pluie d'hier. La tasse cliquette une dernière fois.</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
@@ -14758,8 +14736,7 @@
 narrateur|La petite tasse repose près du banc.
 maman|Ta tasse a fait le voyage.
 papa|Tu as couru, l'eau non.
-narrateur|Ça sent encore la menthe, tout près.
-narrateur|Un papillon passe, puis s'en va.
+narrateur|Le bois sent encore la pluie d'hier.
 narrateur|La tasse cliquette une dernière fois.</t>
         </is>
       </c>
@@ -14963,12 +14940,12 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>La tête bleue ne penche plus. Papa repose l'arrosoir bleu près du banc. Vous avez visé juste. À deux, c'était plus calme. Ça sent encore la menthe, tout près. Un papillon passe, puis s'en va. Le seau d'ombre est rentré sous le banc.</t>
+          <t>La tête bleue ne penche plus. Papa repose l'arrosoir bleu près du banc. Vous avez visé juste. À deux, c'était plus calme. L'ombre du banc a reculé d'un pas. Le seau d'ombre est rentré sous le banc.</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>La tête bleue ne penche plus. Papa repose l'arrosoir bleu près du banc. Vous avez visé juste. À deux, c'était plus calme. Ça sent encore la menthe, tout près. Un papillon passe, puis s'en va. Le seau d'ombre est rentré sous le banc.</t>
+          <t>La tête bleue ne penche plus. Papa repose l'arrosoir bleu près du banc. Vous avez visé juste. À deux, c'était plus calme. L'ombre du banc a reculé d'un pas. Le seau d'ombre est rentré sous le banc.</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
@@ -15107,8 +15084,7 @@
 narrateur|Papa repose l'arrosoir bleu près du banc.
 maman|Vous avez visé juste.
 papa|À deux, c'était plus calme.
-narrateur|Ça sent encore la menthe, tout près.
-narrateur|Un papillon passe, puis s'en va.
+narrateur|L'ombre du banc a reculé d'un pas.
 narrateur|Le seau d'ombre est rentré sous le banc.</t>
         </is>
       </c>
@@ -15507,12 +15483,12 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>On attend les gouttes. Raphaël s'accroupit près du banc. Il penche l'arrosoir bleu, un tout petit peu. Une goutte tombe, puis une autre. Elle boit, tu vois ? La tête bleue se redresse un peu. Raphaël gigote, puis il se tient. Bravo, elle boit. L'arrosoir n'est plus qu'un murmure. Un papillon peut revenir.</t>
+          <t>On attend les gouttes. Raphaël s'accroupit près du banc. Il penche l'arrosoir bleu, un tout petit peu. Une goutte tombe, puis une autre. Elle boit, tu vois ? La tête bleue se redresse un peu. Raphaël gigote, puis il se tient. Bravo, elle boit. L'arrosoir fait à peine plic. Un papillon peut revenir.</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>On attend les gouttes. Raphaël s'accroupit près du banc. Il penche l'arrosoir bleu, un tout petit peu. Une goutte tombe, puis une autre. Elle boit, tu vois ? La tête bleue se redresse un peu. Raphaël gigote, puis il se tient. Bravo, elle boit. L'arrosoir n'est plus qu'un murmure. Un papillon peut revenir.</t>
+          <t>On attend les gouttes. Raphaël s'accroupit près du banc. Il penche l'arrosoir bleu, un tout petit peu. Une goutte tombe, puis une autre. Elle boit, tu vois ? La tête bleue se redresse un peu. Raphaël gigote, puis il se tient. Bravo, elle boit. L'arrosoir fait à peine plic. Un papillon peut revenir.</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
@@ -15655,7 +15631,7 @@
 narrateur|La tête bleue se redresse un peu.
 narrateur|Raphaël gigote, puis il se tient.
 maman|Bravo, elle boit.
-narrateur|L'arrosoir n'est plus qu'un murmure.
+narrateur|L'arrosoir fait à peine plic.
 enfant-m|Un papillon peut revenir.</t>
         </is>
       </c>
@@ -15683,12 +15659,12 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>La tête bleue ne penche plus. Ils restent près du banc, sans bouger beaucoup. La fleur bleue a pris le temps. Tes gouttes sont arrivées. Ça sent encore la menthe, tout près. Un papillon passe, puis s'en va. Une feuille d'ombre a bu, elle aussi.</t>
+          <t>La tête bleue ne penche plus. Ils restent près du banc, sans bouger beaucoup. La fleur bleue a pris le temps. Tes gouttes sont arrivées. Une perle d'eau reste dans l'ombre. Une feuille d'ombre a bu, elle aussi.</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>La tête bleue ne penche plus. Ils restent près du banc, sans bouger beaucoup. La fleur bleue a pris le temps. Tes gouttes sont arrivées. Ça sent encore la menthe, tout près. Un papillon passe, puis s'en va. Une feuille d'ombre a bu, elle aussi.</t>
+          <t>La tête bleue ne penche plus. Ils restent près du banc, sans bouger beaucoup. La fleur bleue a pris le temps. Tes gouttes sont arrivées. Une perle d'eau reste dans l'ombre. Une feuille d'ombre a bu, elle aussi.</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
@@ -15827,8 +15803,7 @@
 narrateur|Ils restent près du banc, sans bouger beaucoup.
 maman|La fleur bleue a pris le temps.
 papa|Tes gouttes sont arrivées.
-narrateur|Ça sent encore la menthe, tout près.
-narrateur|Un papillon passe, puis s'en va.
+narrateur|Une perle d'eau reste dans l'ombre.
 narrateur|Une feuille d'ombre a bu, elle aussi.</t>
         </is>
       </c>
@@ -16032,12 +16007,12 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>La tête bleue ne penche plus. La petite tasse repose près du banc. Ta tasse a fait le voyage. Tu as couru, l'eau non. Ça sent encore la menthe, tout près. Un papillon passe, puis s'en va. Le papillon a suivi la tasse, puis parti.</t>
+          <t>La tête bleue ne penche plus. La petite tasse repose près du banc. Ta tasse a fait le voyage. Tu as couru, l'eau non. Le bois sent encore la pluie d'hier. Le papillon a suivi la tasse, puis parti.</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>La tête bleue ne penche plus. La petite tasse repose près du banc. Ta tasse a fait le voyage. Tu as couru, l'eau non. Ça sent encore la menthe, tout près. Un papillon passe, puis s'en va. Le papillon a suivi la tasse, puis parti.</t>
+          <t>La tête bleue ne penche plus. La petite tasse repose près du banc. Ta tasse a fait le voyage. Tu as couru, l'eau non. Le bois sent encore la pluie d'hier. Le papillon a suivi la tasse, puis parti.</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
@@ -16176,8 +16151,7 @@
 narrateur|La petite tasse repose près du banc.
 maman|Ta tasse a fait le voyage.
 papa|Tu as couru, l'eau non.
-narrateur|Ça sent encore la menthe, tout près.
-narrateur|Un papillon passe, puis s'en va.
+narrateur|Le bois sent encore la pluie d'hier.
 narrateur|Le papillon a suivi la tasse, puis parti.</t>
         </is>
       </c>
@@ -16381,12 +16355,12 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>La tête bleue ne penche plus. Papa repose l'arrosoir bleu près du banc. Vous avez visé juste. À deux, c'était plus calme. Ça sent encore la menthe, tout près. Un papillon passe, puis s'en va. Le bois du banc a séché, tout doux.</t>
+          <t>La tête bleue ne penche plus. Papa repose l'arrosoir bleu près du banc. Vous avez visé juste. À deux, c'était plus calme. L'ombre du banc a reculé d'un pas. Le bois du banc a séché, tout doux.</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>La tête bleue ne penche plus. Papa repose l'arrosoir bleu près du banc. Vous avez visé juste. À deux, c'était plus calme. Ça sent encore la menthe, tout près. Un papillon passe, puis s'en va. Le bois du banc a séché, tout doux.</t>
+          <t>La tête bleue ne penche plus. Papa repose l'arrosoir bleu près du banc. Vous avez visé juste. À deux, c'était plus calme. L'ombre du banc a reculé d'un pas. Le bois du banc a séché, tout doux.</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
@@ -16525,8 +16499,7 @@
 narrateur|Papa repose l'arrosoir bleu près du banc.
 maman|Vous avez visé juste.
 papa|À deux, c'était plus calme.
-narrateur|Ça sent encore la menthe, tout près.
-narrateur|Un papillon passe, puis s'en va.
+narrateur|L'ombre du banc a reculé d'un pas.
 narrateur|Le bois du banc a séché, tout doux.</t>
         </is>
       </c>
@@ -16548,7 +16521,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A7"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16598,6 +16571,13 @@
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
